--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\used_cars_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C637CD-AF15-47C9-80A7-1D736FB43092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFFE6AEF-69CB-4C5C-A54C-A5D0B5D31A05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D7CE9FC5-F49F-40D4-93B4-AA39BB343A99}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$F$963</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$F$1111</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2892" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3213" uniqueCount="20">
   <si>
     <t>Date</t>
   </si>
@@ -96,6 +96,12 @@
   </si>
   <si>
     <t>Dealer</t>
+  </si>
+  <si>
+    <t>Nashik-pmax-Used-car-16june</t>
+  </si>
+  <si>
+    <t>UC-DSA-Nashik-UsedCars</t>
   </si>
 </sst>
 </file>
@@ -468,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22A7DA2E-DF85-4559-9E8B-F6EDBCD02D26}">
-  <dimension ref="A1:F963"/>
+  <dimension ref="A1:F1111"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -5107,10 +5113,10 @@
         <v>17</v>
       </c>
       <c r="D232">
+        <v>29</v>
+      </c>
+      <c r="E232">
         <v>28</v>
-      </c>
-      <c r="E232">
-        <v>27</v>
       </c>
       <c r="F232" t="s">
         <v>10</v>
@@ -8427,10 +8433,10 @@
         <v>15</v>
       </c>
       <c r="D398">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E398">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F398" t="s">
         <v>6</v>
@@ -8607,7 +8613,7 @@
         <v>15</v>
       </c>
       <c r="D407">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E407">
         <v>15</v>
@@ -9107,10 +9113,10 @@
         <v>15</v>
       </c>
       <c r="D432">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E432">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F432" t="s">
         <v>6</v>
@@ -10167,7 +10173,7 @@
         <v>17</v>
       </c>
       <c r="D485">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E485">
         <v>7</v>
@@ -12207,10 +12213,10 @@
         <v>16</v>
       </c>
       <c r="D587">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E587">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F587" t="s">
         <v>8</v>
@@ -13287,10 +13293,10 @@
         <v>17</v>
       </c>
       <c r="D641">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E641">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F641" t="s">
         <v>6</v>
@@ -13347,10 +13353,10 @@
         <v>17</v>
       </c>
       <c r="D644">
+        <v>30</v>
+      </c>
+      <c r="E644">
         <v>29</v>
-      </c>
-      <c r="E644">
-        <v>28</v>
       </c>
       <c r="F644" t="s">
         <v>6</v>
@@ -14947,7 +14953,7 @@
         <v>17</v>
       </c>
       <c r="D724">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E724">
         <v>14</v>
@@ -16227,10 +16233,10 @@
         <v>16</v>
       </c>
       <c r="D788">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E788">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F788" t="s">
         <v>8</v>
@@ -16287,10 +16293,10 @@
         <v>16</v>
       </c>
       <c r="D791">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E791">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F791" t="s">
         <v>10</v>
@@ -16307,10 +16313,10 @@
         <v>17</v>
       </c>
       <c r="D792">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E792">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F792" t="s">
         <v>10</v>
@@ -16387,10 +16393,10 @@
         <v>15</v>
       </c>
       <c r="D796">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E796">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F796" t="s">
         <v>6</v>
@@ -16407,10 +16413,10 @@
         <v>16</v>
       </c>
       <c r="D797">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E797">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F797" t="s">
         <v>6</v>
@@ -16447,10 +16453,10 @@
         <v>15</v>
       </c>
       <c r="D799">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E799">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F799" t="s">
         <v>6</v>
@@ -17547,10 +17553,10 @@
         <v>17</v>
       </c>
       <c r="D854">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E854">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F854" t="s">
         <v>8</v>
@@ -19736,8 +19742,2271 @@
         <v>10</v>
       </c>
     </row>
+    <row r="964" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A964" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B964" t="s">
+        <v>5</v>
+      </c>
+      <c r="C964" t="s">
+        <v>17</v>
+      </c>
+      <c r="D964">
+        <v>6</v>
+      </c>
+      <c r="E964">
+        <v>4</v>
+      </c>
+      <c r="F964" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="965" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A965" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B965" t="s">
+        <v>5</v>
+      </c>
+      <c r="C965" t="s">
+        <v>15</v>
+      </c>
+      <c r="D965">
+        <v>3</v>
+      </c>
+      <c r="E965">
+        <v>3</v>
+      </c>
+      <c r="F965" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="966" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A966" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B966" t="s">
+        <v>13</v>
+      </c>
+      <c r="C966" t="s">
+        <v>17</v>
+      </c>
+      <c r="D966">
+        <v>21</v>
+      </c>
+      <c r="E966">
+        <v>20</v>
+      </c>
+      <c r="F966" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="967" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A967" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B967" t="s">
+        <v>13</v>
+      </c>
+      <c r="C967" t="s">
+        <v>15</v>
+      </c>
+      <c r="D967">
+        <v>4</v>
+      </c>
+      <c r="E967">
+        <v>4</v>
+      </c>
+      <c r="F967" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="968" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A968" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B968" t="s">
+        <v>13</v>
+      </c>
+      <c r="C968" t="s">
+        <v>16</v>
+      </c>
+      <c r="D968">
+        <v>15</v>
+      </c>
+      <c r="E968">
+        <v>9</v>
+      </c>
+      <c r="F968" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="969" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A969" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B969" t="s">
+        <v>12</v>
+      </c>
+      <c r="C969" t="s">
+        <v>17</v>
+      </c>
+      <c r="D969">
+        <v>9</v>
+      </c>
+      <c r="E969">
+        <v>8</v>
+      </c>
+      <c r="F969" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="970" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A970" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B970" t="s">
+        <v>12</v>
+      </c>
+      <c r="C970" t="s">
+        <v>16</v>
+      </c>
+      <c r="D970">
+        <v>2</v>
+      </c>
+      <c r="E970">
+        <v>2</v>
+      </c>
+      <c r="F970" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="971" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A971" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B971" t="s">
+        <v>7</v>
+      </c>
+      <c r="C971" t="s">
+        <v>17</v>
+      </c>
+      <c r="D971">
+        <v>7</v>
+      </c>
+      <c r="E971">
+        <v>6</v>
+      </c>
+      <c r="F971" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="972" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A972" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B972" t="s">
+        <v>7</v>
+      </c>
+      <c r="C972" t="s">
+        <v>15</v>
+      </c>
+      <c r="D972">
+        <v>5</v>
+      </c>
+      <c r="E972">
+        <v>5</v>
+      </c>
+      <c r="F972" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="973" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A973" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B973" t="s">
+        <v>7</v>
+      </c>
+      <c r="C973" t="s">
+        <v>16</v>
+      </c>
+      <c r="D973">
+        <v>2</v>
+      </c>
+      <c r="E973">
+        <v>2</v>
+      </c>
+      <c r="F973" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="974" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A974" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B974" t="s">
+        <v>11</v>
+      </c>
+      <c r="C974" t="s">
+        <v>17</v>
+      </c>
+      <c r="D974">
+        <v>20</v>
+      </c>
+      <c r="E974">
+        <v>20</v>
+      </c>
+      <c r="F974" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="975" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A975" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B975" t="s">
+        <v>11</v>
+      </c>
+      <c r="C975" t="s">
+        <v>16</v>
+      </c>
+      <c r="D975">
+        <v>7</v>
+      </c>
+      <c r="E975">
+        <v>5</v>
+      </c>
+      <c r="F975" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="976" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A976" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B976" t="s">
+        <v>9</v>
+      </c>
+      <c r="C976" t="s">
+        <v>17</v>
+      </c>
+      <c r="D976">
+        <v>24</v>
+      </c>
+      <c r="E976">
+        <v>23</v>
+      </c>
+      <c r="F976" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="977" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A977" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B977" t="s">
+        <v>9</v>
+      </c>
+      <c r="C977" t="s">
+        <v>15</v>
+      </c>
+      <c r="D977">
+        <v>4</v>
+      </c>
+      <c r="E977">
+        <v>4</v>
+      </c>
+      <c r="F977" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="978" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A978" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B978" t="s">
+        <v>9</v>
+      </c>
+      <c r="C978" t="s">
+        <v>16</v>
+      </c>
+      <c r="D978">
+        <v>2</v>
+      </c>
+      <c r="E978">
+        <v>2</v>
+      </c>
+      <c r="F978" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="979" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A979" s="1">
+        <v>46186</v>
+      </c>
+      <c r="B979" t="s">
+        <v>5</v>
+      </c>
+      <c r="C979" t="s">
+        <v>17</v>
+      </c>
+      <c r="D979">
+        <v>14</v>
+      </c>
+      <c r="E979">
+        <v>13</v>
+      </c>
+      <c r="F979" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="980" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A980" s="1">
+        <v>46186</v>
+      </c>
+      <c r="B980" t="s">
+        <v>5</v>
+      </c>
+      <c r="C980" t="s">
+        <v>15</v>
+      </c>
+      <c r="D980">
+        <v>5</v>
+      </c>
+      <c r="E980">
+        <v>5</v>
+      </c>
+      <c r="F980" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="981" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A981" s="1">
+        <v>46186</v>
+      </c>
+      <c r="B981" t="s">
+        <v>5</v>
+      </c>
+      <c r="C981" t="s">
+        <v>16</v>
+      </c>
+      <c r="D981">
+        <v>4</v>
+      </c>
+      <c r="E981">
+        <v>2</v>
+      </c>
+      <c r="F981" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="982" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A982" s="1">
+        <v>46186</v>
+      </c>
+      <c r="B982" t="s">
+        <v>13</v>
+      </c>
+      <c r="C982" t="s">
+        <v>17</v>
+      </c>
+      <c r="D982">
+        <v>23</v>
+      </c>
+      <c r="E982">
+        <v>23</v>
+      </c>
+      <c r="F982" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="983" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A983" s="1">
+        <v>46186</v>
+      </c>
+      <c r="B983" t="s">
+        <v>13</v>
+      </c>
+      <c r="C983" t="s">
+        <v>15</v>
+      </c>
+      <c r="D983">
+        <v>12</v>
+      </c>
+      <c r="E983">
+        <v>9</v>
+      </c>
+      <c r="F983" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="984" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A984" s="1">
+        <v>46186</v>
+      </c>
+      <c r="B984" t="s">
+        <v>13</v>
+      </c>
+      <c r="C984" t="s">
+        <v>16</v>
+      </c>
+      <c r="D984">
+        <v>15</v>
+      </c>
+      <c r="E984">
+        <v>6</v>
+      </c>
+      <c r="F984" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="985" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A985" s="1">
+        <v>46186</v>
+      </c>
+      <c r="B985" t="s">
+        <v>12</v>
+      </c>
+      <c r="C985" t="s">
+        <v>17</v>
+      </c>
+      <c r="D985">
+        <v>17</v>
+      </c>
+      <c r="E985">
+        <v>14</v>
+      </c>
+      <c r="F985" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="986" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A986" s="1">
+        <v>46186</v>
+      </c>
+      <c r="B986" t="s">
+        <v>12</v>
+      </c>
+      <c r="C986" t="s">
+        <v>15</v>
+      </c>
+      <c r="D986">
+        <v>2</v>
+      </c>
+      <c r="E986">
+        <v>2</v>
+      </c>
+      <c r="F986" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="987" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A987" s="1">
+        <v>46186</v>
+      </c>
+      <c r="B987" t="s">
+        <v>12</v>
+      </c>
+      <c r="C987" t="s">
+        <v>16</v>
+      </c>
+      <c r="D987">
+        <v>3</v>
+      </c>
+      <c r="E987">
+        <v>3</v>
+      </c>
+      <c r="F987" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="988" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A988" s="1">
+        <v>46186</v>
+      </c>
+      <c r="B988" t="s">
+        <v>7</v>
+      </c>
+      <c r="C988" t="s">
+        <v>17</v>
+      </c>
+      <c r="D988">
+        <v>14</v>
+      </c>
+      <c r="E988">
+        <v>13</v>
+      </c>
+      <c r="F988" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="989" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A989" s="1">
+        <v>46186</v>
+      </c>
+      <c r="B989" t="s">
+        <v>7</v>
+      </c>
+      <c r="C989" t="s">
+        <v>15</v>
+      </c>
+      <c r="D989">
+        <v>5</v>
+      </c>
+      <c r="E989">
+        <v>5</v>
+      </c>
+      <c r="F989" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="990" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A990" s="1">
+        <v>46186</v>
+      </c>
+      <c r="B990" t="s">
+        <v>7</v>
+      </c>
+      <c r="C990" t="s">
+        <v>16</v>
+      </c>
+      <c r="D990">
+        <v>3</v>
+      </c>
+      <c r="E990">
+        <v>2</v>
+      </c>
+      <c r="F990" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="991" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A991" s="1">
+        <v>46186</v>
+      </c>
+      <c r="B991" t="s">
+        <v>11</v>
+      </c>
+      <c r="C991" t="s">
+        <v>17</v>
+      </c>
+      <c r="D991">
+        <v>22</v>
+      </c>
+      <c r="E991">
+        <v>21</v>
+      </c>
+      <c r="F991" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="992" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A992" s="1">
+        <v>46186</v>
+      </c>
+      <c r="B992" t="s">
+        <v>11</v>
+      </c>
+      <c r="C992" t="s">
+        <v>15</v>
+      </c>
+      <c r="D992">
+        <v>2</v>
+      </c>
+      <c r="E992">
+        <v>2</v>
+      </c>
+      <c r="F992" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="993" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A993" s="1">
+        <v>46186</v>
+      </c>
+      <c r="B993" t="s">
+        <v>11</v>
+      </c>
+      <c r="C993" t="s">
+        <v>16</v>
+      </c>
+      <c r="D993">
+        <v>2</v>
+      </c>
+      <c r="E993">
+        <v>2</v>
+      </c>
+      <c r="F993" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="994" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A994" s="1">
+        <v>46186</v>
+      </c>
+      <c r="B994" t="s">
+        <v>9</v>
+      </c>
+      <c r="C994" t="s">
+        <v>17</v>
+      </c>
+      <c r="D994">
+        <v>27</v>
+      </c>
+      <c r="E994">
+        <v>27</v>
+      </c>
+      <c r="F994" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="995" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A995" s="1">
+        <v>46186</v>
+      </c>
+      <c r="B995" t="s">
+        <v>9</v>
+      </c>
+      <c r="C995" t="s">
+        <v>15</v>
+      </c>
+      <c r="D995">
+        <v>1</v>
+      </c>
+      <c r="E995">
+        <v>1</v>
+      </c>
+      <c r="F995" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="996" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A996" s="1">
+        <v>46186</v>
+      </c>
+      <c r="B996" t="s">
+        <v>9</v>
+      </c>
+      <c r="C996" t="s">
+        <v>16</v>
+      </c>
+      <c r="D996">
+        <v>2</v>
+      </c>
+      <c r="E996">
+        <v>1</v>
+      </c>
+      <c r="F996" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="997" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A997" s="1">
+        <v>46187</v>
+      </c>
+      <c r="B997" t="s">
+        <v>5</v>
+      </c>
+      <c r="C997" t="s">
+        <v>17</v>
+      </c>
+      <c r="D997">
+        <v>6</v>
+      </c>
+      <c r="E997">
+        <v>6</v>
+      </c>
+      <c r="F997" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="998" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A998" s="1">
+        <v>46187</v>
+      </c>
+      <c r="B998" t="s">
+        <v>5</v>
+      </c>
+      <c r="C998" t="s">
+        <v>15</v>
+      </c>
+      <c r="D998">
+        <v>7</v>
+      </c>
+      <c r="E998">
+        <v>7</v>
+      </c>
+      <c r="F998" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="999" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A999" s="1">
+        <v>46187</v>
+      </c>
+      <c r="B999" t="s">
+        <v>5</v>
+      </c>
+      <c r="C999" t="s">
+        <v>16</v>
+      </c>
+      <c r="D999">
+        <v>9</v>
+      </c>
+      <c r="E999">
+        <v>4</v>
+      </c>
+      <c r="F999" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1000" s="1">
+        <v>46187</v>
+      </c>
+      <c r="B1000" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1000" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1000">
+        <v>20</v>
+      </c>
+      <c r="E1000">
+        <v>19</v>
+      </c>
+      <c r="F1000" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1001" s="1">
+        <v>46187</v>
+      </c>
+      <c r="B1001" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1001" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1001">
+        <v>6</v>
+      </c>
+      <c r="E1001">
+        <v>5</v>
+      </c>
+      <c r="F1001" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1002" s="1">
+        <v>46187</v>
+      </c>
+      <c r="B1002" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1002" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1002">
+        <v>2</v>
+      </c>
+      <c r="E1002">
+        <v>2</v>
+      </c>
+      <c r="F1002" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1003" s="1">
+        <v>46187</v>
+      </c>
+      <c r="B1003" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1003" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1003">
+        <v>6</v>
+      </c>
+      <c r="E1003">
+        <v>5</v>
+      </c>
+      <c r="F1003" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1004" s="1">
+        <v>46187</v>
+      </c>
+      <c r="B1004" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1004" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1004">
+        <v>2</v>
+      </c>
+      <c r="E1004">
+        <v>2</v>
+      </c>
+      <c r="F1004" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1005" s="1">
+        <v>46187</v>
+      </c>
+      <c r="B1005" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1005" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1005">
+        <v>16</v>
+      </c>
+      <c r="E1005">
+        <v>12</v>
+      </c>
+      <c r="F1005" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1006" s="1">
+        <v>46187</v>
+      </c>
+      <c r="B1006" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1006" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1006">
+        <v>11</v>
+      </c>
+      <c r="E1006">
+        <v>8</v>
+      </c>
+      <c r="F1006" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1007" s="1">
+        <v>46187</v>
+      </c>
+      <c r="B1007" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1007" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1007">
+        <v>9</v>
+      </c>
+      <c r="E1007">
+        <v>8</v>
+      </c>
+      <c r="F1007" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1008" s="1">
+        <v>46187</v>
+      </c>
+      <c r="B1008" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1008" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1008">
+        <v>36</v>
+      </c>
+      <c r="E1008">
+        <v>35</v>
+      </c>
+      <c r="F1008" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1009" s="1">
+        <v>46187</v>
+      </c>
+      <c r="B1009" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1009" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1009">
+        <v>7</v>
+      </c>
+      <c r="E1009">
+        <v>7</v>
+      </c>
+      <c r="F1009" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1010" s="1">
+        <v>46187</v>
+      </c>
+      <c r="B1010" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1010" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1010">
+        <v>16</v>
+      </c>
+      <c r="E1010">
+        <v>11</v>
+      </c>
+      <c r="F1010" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1011" s="1">
+        <v>46187</v>
+      </c>
+      <c r="B1011" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1011" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1011">
+        <v>18</v>
+      </c>
+      <c r="E1011">
+        <v>16</v>
+      </c>
+      <c r="F1011" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1012" s="1">
+        <v>46187</v>
+      </c>
+      <c r="B1012" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1012" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1012">
+        <v>1</v>
+      </c>
+      <c r="E1012">
+        <v>1</v>
+      </c>
+      <c r="F1012" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1013" s="1">
+        <v>46187</v>
+      </c>
+      <c r="B1013" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1013" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1013">
+        <v>2</v>
+      </c>
+      <c r="E1013">
+        <v>2</v>
+      </c>
+      <c r="F1013" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1014" s="1">
+        <v>46188</v>
+      </c>
+      <c r="B1014" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1014" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1014">
+        <v>12</v>
+      </c>
+      <c r="E1014">
+        <v>9</v>
+      </c>
+      <c r="F1014" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1015" s="1">
+        <v>46188</v>
+      </c>
+      <c r="B1015" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1015" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1015">
+        <v>6</v>
+      </c>
+      <c r="E1015">
+        <v>5</v>
+      </c>
+      <c r="F1015" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1016" s="1">
+        <v>46188</v>
+      </c>
+      <c r="B1016" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1016" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1016">
+        <v>7</v>
+      </c>
+      <c r="E1016">
+        <v>5</v>
+      </c>
+      <c r="F1016" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1017" s="1">
+        <v>46188</v>
+      </c>
+      <c r="B1017" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1017" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1017">
+        <v>13</v>
+      </c>
+      <c r="E1017">
+        <v>13</v>
+      </c>
+      <c r="F1017" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1018" s="1">
+        <v>46188</v>
+      </c>
+      <c r="B1018" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1018" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1018">
+        <v>5</v>
+      </c>
+      <c r="E1018">
+        <v>5</v>
+      </c>
+      <c r="F1018" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1019" s="1">
+        <v>46188</v>
+      </c>
+      <c r="B1019" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1019" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1019">
+        <v>5</v>
+      </c>
+      <c r="E1019">
+        <v>5</v>
+      </c>
+      <c r="F1019" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1020" s="1">
+        <v>46188</v>
+      </c>
+      <c r="B1020" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1020" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1020">
+        <v>2</v>
+      </c>
+      <c r="E1020">
+        <v>2</v>
+      </c>
+      <c r="F1020" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1021" s="1">
+        <v>46188</v>
+      </c>
+      <c r="B1021" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1021" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1021">
+        <v>2</v>
+      </c>
+      <c r="E1021">
+        <v>2</v>
+      </c>
+      <c r="F1021" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1022" s="1">
+        <v>46188</v>
+      </c>
+      <c r="B1022" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1022" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1022">
+        <v>4</v>
+      </c>
+      <c r="E1022">
+        <v>4</v>
+      </c>
+      <c r="F1022" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1023" s="1">
+        <v>46188</v>
+      </c>
+      <c r="B1023" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1023" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1023">
+        <v>1</v>
+      </c>
+      <c r="E1023">
+        <v>1</v>
+      </c>
+      <c r="F1023" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1024" s="1">
+        <v>46188</v>
+      </c>
+      <c r="B1024" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1024" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1024">
+        <v>12</v>
+      </c>
+      <c r="E1024">
+        <v>4</v>
+      </c>
+      <c r="F1024" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1025" s="1">
+        <v>46188</v>
+      </c>
+      <c r="B1025" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1025" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1025">
+        <v>23</v>
+      </c>
+      <c r="E1025">
+        <v>20</v>
+      </c>
+      <c r="F1025" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1026" s="1">
+        <v>46188</v>
+      </c>
+      <c r="B1026" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1026" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1026">
+        <v>1</v>
+      </c>
+      <c r="E1026">
+        <v>1</v>
+      </c>
+      <c r="F1026" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1027" s="1">
+        <v>46188</v>
+      </c>
+      <c r="B1027" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1027" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1027">
+        <v>1</v>
+      </c>
+      <c r="E1027">
+        <v>1</v>
+      </c>
+      <c r="F1027" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1028" s="1">
+        <v>46188</v>
+      </c>
+      <c r="B1028" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1028" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1028">
+        <v>10</v>
+      </c>
+      <c r="E1028">
+        <v>10</v>
+      </c>
+      <c r="F1028" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1029" s="1">
+        <v>46188</v>
+      </c>
+      <c r="B1029" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1029" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1029">
+        <v>1</v>
+      </c>
+      <c r="E1029">
+        <v>1</v>
+      </c>
+      <c r="F1029" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1030" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B1030" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1030" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1030">
+        <v>8</v>
+      </c>
+      <c r="E1030">
+        <v>8</v>
+      </c>
+      <c r="F1030" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1031" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B1031" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1031" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1031">
+        <v>8</v>
+      </c>
+      <c r="E1031">
+        <v>7</v>
+      </c>
+      <c r="F1031" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1032" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B1032" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1032" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1032">
+        <v>9</v>
+      </c>
+      <c r="E1032">
+        <v>5</v>
+      </c>
+      <c r="F1032" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1033" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B1033" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1033" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1033">
+        <v>24</v>
+      </c>
+      <c r="E1033">
+        <v>22</v>
+      </c>
+      <c r="F1033" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1034" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B1034" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1034" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1034">
+        <v>15</v>
+      </c>
+      <c r="E1034">
+        <v>14</v>
+      </c>
+      <c r="F1034" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1035" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B1035" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1035" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1035">
+        <v>9</v>
+      </c>
+      <c r="E1035">
+        <v>5</v>
+      </c>
+      <c r="F1035" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1036" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B1036" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1036" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1036">
+        <v>9</v>
+      </c>
+      <c r="E1036">
+        <v>8</v>
+      </c>
+      <c r="F1036" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1037" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B1037" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1037" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1037">
+        <v>8</v>
+      </c>
+      <c r="E1037">
+        <v>7</v>
+      </c>
+      <c r="F1037" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1038" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B1038" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1038" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1038">
+        <v>10</v>
+      </c>
+      <c r="E1038">
+        <v>9</v>
+      </c>
+      <c r="F1038" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1039" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B1039" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1039" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1039">
+        <v>2</v>
+      </c>
+      <c r="E1039">
+        <v>2</v>
+      </c>
+      <c r="F1039" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1040" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B1040" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1040" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1040">
+        <v>4</v>
+      </c>
+      <c r="E1040">
+        <v>3</v>
+      </c>
+      <c r="F1040" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1041" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B1041" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1041" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1041">
+        <v>2</v>
+      </c>
+      <c r="E1041">
+        <v>2</v>
+      </c>
+      <c r="F1041" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1042" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B1042" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1042" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1042">
+        <v>2</v>
+      </c>
+      <c r="E1042">
+        <v>2</v>
+      </c>
+      <c r="F1042" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1043" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B1043" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1043" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1043">
+        <v>25</v>
+      </c>
+      <c r="E1043">
+        <v>22</v>
+      </c>
+      <c r="F1043" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1044" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B1044" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1044" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1044">
+        <v>11</v>
+      </c>
+      <c r="E1044">
+        <v>9</v>
+      </c>
+      <c r="F1044" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1045" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B1045" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1045" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1045">
+        <v>7</v>
+      </c>
+      <c r="E1045">
+        <v>7</v>
+      </c>
+      <c r="F1045" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1046" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B1046" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1046" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1046">
+        <v>1</v>
+      </c>
+      <c r="E1046">
+        <v>1</v>
+      </c>
+      <c r="F1046" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1047" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B1047" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1047" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1047">
+        <v>2</v>
+      </c>
+      <c r="E1047">
+        <v>1</v>
+      </c>
+      <c r="F1047" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1048" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B1048" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1048" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1048">
+        <v>1</v>
+      </c>
+      <c r="E1048">
+        <v>1</v>
+      </c>
+      <c r="F1048" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1049" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B1049" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1049" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1049">
+        <v>1</v>
+      </c>
+      <c r="E1049">
+        <v>1</v>
+      </c>
+      <c r="F1049" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1050" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B1050" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1050" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1050">
+        <v>7</v>
+      </c>
+      <c r="E1050">
+        <v>7</v>
+      </c>
+      <c r="F1050" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1051" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B1051" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1051" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1051">
+        <v>8</v>
+      </c>
+      <c r="E1051">
+        <v>6</v>
+      </c>
+      <c r="F1051" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1052" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B1052" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1052" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1052">
+        <v>3</v>
+      </c>
+      <c r="E1052">
+        <v>3</v>
+      </c>
+      <c r="F1052" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1053" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B1053" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1053" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1053">
+        <v>11</v>
+      </c>
+      <c r="E1053">
+        <v>11</v>
+      </c>
+      <c r="F1053" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1054" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B1054" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1054" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1054">
+        <v>7</v>
+      </c>
+      <c r="E1054">
+        <v>6</v>
+      </c>
+      <c r="F1054" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1055" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B1055" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1055" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1055">
+        <v>6</v>
+      </c>
+      <c r="E1055">
+        <v>5</v>
+      </c>
+      <c r="F1055" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1056" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B1056" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1056" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1056">
+        <v>6</v>
+      </c>
+      <c r="E1056">
+        <v>6</v>
+      </c>
+      <c r="F1056" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1057" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B1057" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1057" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1057">
+        <v>5</v>
+      </c>
+      <c r="E1057">
+        <v>5</v>
+      </c>
+      <c r="F1057" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1058" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B1058" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1058" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1058">
+        <v>11</v>
+      </c>
+      <c r="E1058">
+        <v>8</v>
+      </c>
+      <c r="F1058" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1059" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B1059" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1059" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1059">
+        <v>1</v>
+      </c>
+      <c r="E1059">
+        <v>1</v>
+      </c>
+      <c r="F1059" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1060" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B1060" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1060" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1060">
+        <v>2</v>
+      </c>
+      <c r="E1060">
+        <v>2</v>
+      </c>
+      <c r="F1060" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1061" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B1061" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1061" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1061">
+        <v>4</v>
+      </c>
+      <c r="E1061">
+        <v>4</v>
+      </c>
+      <c r="F1061" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1062" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B1062" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1062" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1062">
+        <v>2</v>
+      </c>
+      <c r="E1062">
+        <v>2</v>
+      </c>
+      <c r="F1062" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1063" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B1063" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1063" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1063">
+        <v>36</v>
+      </c>
+      <c r="E1063">
+        <v>34</v>
+      </c>
+      <c r="F1063" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1064" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B1064" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1064" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1064">
+        <v>4</v>
+      </c>
+      <c r="E1064">
+        <v>4</v>
+      </c>
+      <c r="F1064" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1065" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B1065" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1065" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1065">
+        <v>4</v>
+      </c>
+      <c r="E1065">
+        <v>4</v>
+      </c>
+      <c r="F1065" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1066" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B1066" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1066" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1066">
+        <v>2</v>
+      </c>
+      <c r="E1066">
+        <v>2</v>
+      </c>
+      <c r="F1066" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1067" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B1067" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1067" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1067">
+        <v>1</v>
+      </c>
+      <c r="E1067">
+        <v>0</v>
+      </c>
+      <c r="F1067" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1068" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B1068" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1068" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1068">
+        <v>6</v>
+      </c>
+      <c r="E1068">
+        <v>6</v>
+      </c>
+      <c r="F1068" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1069" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B1069" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1069" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1069">
+        <v>6</v>
+      </c>
+      <c r="E1069">
+        <v>5</v>
+      </c>
+      <c r="F1069" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1070" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B1070" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1070" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1070">
+        <v>2</v>
+      </c>
+      <c r="E1070">
+        <v>2</v>
+      </c>
+      <c r="F1070" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1071" s="1"/>
+    </row>
+    <row r="1072" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1072" s="1"/>
+    </row>
+    <row r="1073" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1073" s="1"/>
+    </row>
+    <row r="1074" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1074" s="1"/>
+    </row>
+    <row r="1075" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1075" s="1"/>
+    </row>
+    <row r="1076" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1076" s="1"/>
+    </row>
+    <row r="1077" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1077" s="1"/>
+    </row>
+    <row r="1078" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1078" s="1"/>
+    </row>
+    <row r="1079" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1079" s="1"/>
+    </row>
+    <row r="1080" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1080" s="1"/>
+    </row>
+    <row r="1081" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1081" s="1"/>
+    </row>
+    <row r="1082" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1082" s="1"/>
+    </row>
+    <row r="1083" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1083" s="1"/>
+    </row>
+    <row r="1084" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1084" s="1"/>
+    </row>
+    <row r="1085" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1085" s="1"/>
+    </row>
+    <row r="1086" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1086" s="1"/>
+    </row>
+    <row r="1087" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1087" s="1"/>
+    </row>
+    <row r="1088" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1088" s="1"/>
+    </row>
+    <row r="1089" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1089" s="1"/>
+    </row>
+    <row r="1090" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1090" s="1"/>
+    </row>
+    <row r="1091" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1091" s="1"/>
+    </row>
+    <row r="1092" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1092" s="1"/>
+    </row>
+    <row r="1093" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1093" s="1"/>
+    </row>
+    <row r="1094" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1094" s="1"/>
+    </row>
+    <row r="1095" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1095" s="1"/>
+    </row>
+    <row r="1096" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1096" s="1"/>
+    </row>
+    <row r="1097" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1097" s="1"/>
+    </row>
+    <row r="1098" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1098" s="1"/>
+    </row>
+    <row r="1099" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1099" s="1"/>
+    </row>
+    <row r="1100" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1100" s="1"/>
+    </row>
+    <row r="1101" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1101" s="1"/>
+    </row>
+    <row r="1102" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1102" s="1"/>
+    </row>
+    <row r="1103" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1103" s="1"/>
+    </row>
+    <row r="1104" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1104" s="1"/>
+    </row>
+    <row r="1105" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1105" s="1"/>
+    </row>
+    <row r="1106" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1106" s="1"/>
+    </row>
+    <row r="1107" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1107" s="1"/>
+    </row>
+    <row r="1108" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1108" s="1"/>
+    </row>
+    <row r="1109" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1109" s="1"/>
+    </row>
+    <row r="1110" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1110" s="1"/>
+    </row>
+    <row r="1111" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1111" s="1"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F963" xr:uid="{22A7DA2E-DF85-4559-9E8B-F6EDBCD02D26}"/>
+  <autoFilter ref="A1:F1111" xr:uid="{22A7DA2E-DF85-4559-9E8B-F6EDBCD02D26}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\used_cars_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFFE6AEF-69CB-4C5C-A54C-A5D0B5D31A05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4013C78-2D74-43BA-8626-97BCAE3C12DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D7CE9FC5-F49F-40D4-93B4-AA39BB343A99}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3213" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3393" uniqueCount="20">
   <si>
     <t>Date</t>
   </si>
@@ -474,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22A7DA2E-DF85-4559-9E8B-F6EDBCD02D26}">
-  <dimension ref="A1:F1111"/>
+  <dimension ref="A1:F1130"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -21883,130 +21883,1206 @@
       </c>
     </row>
     <row r="1071" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1071" s="1"/>
+      <c r="A1071" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B1071" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1071" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1071">
+        <v>3</v>
+      </c>
+      <c r="E1071">
+        <v>3</v>
+      </c>
+      <c r="F1071" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="1072" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1072" s="1"/>
-    </row>
-    <row r="1073" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1073" s="1"/>
-    </row>
-    <row r="1074" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1074" s="1"/>
-    </row>
-    <row r="1075" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1075" s="1"/>
-    </row>
-    <row r="1076" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1076" s="1"/>
-    </row>
-    <row r="1077" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1077" s="1"/>
-    </row>
-    <row r="1078" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1078" s="1"/>
-    </row>
-    <row r="1079" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1079" s="1"/>
-    </row>
-    <row r="1080" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1080" s="1"/>
-    </row>
-    <row r="1081" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1081" s="1"/>
-    </row>
-    <row r="1082" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1082" s="1"/>
-    </row>
-    <row r="1083" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1083" s="1"/>
-    </row>
-    <row r="1084" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1084" s="1"/>
-    </row>
-    <row r="1085" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1085" s="1"/>
-    </row>
-    <row r="1086" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1086" s="1"/>
-    </row>
-    <row r="1087" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1087" s="1"/>
-    </row>
-    <row r="1088" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1088" s="1"/>
-    </row>
-    <row r="1089" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1089" s="1"/>
-    </row>
-    <row r="1090" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1090" s="1"/>
-    </row>
-    <row r="1091" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1091" s="1"/>
-    </row>
-    <row r="1092" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1092" s="1"/>
-    </row>
-    <row r="1093" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1093" s="1"/>
-    </row>
-    <row r="1094" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1094" s="1"/>
-    </row>
-    <row r="1095" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1095" s="1"/>
-    </row>
-    <row r="1096" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1096" s="1"/>
-    </row>
-    <row r="1097" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1097" s="1"/>
-    </row>
-    <row r="1098" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1098" s="1"/>
-    </row>
-    <row r="1099" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1099" s="1"/>
-    </row>
-    <row r="1100" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1100" s="1"/>
-    </row>
-    <row r="1101" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1101" s="1"/>
-    </row>
-    <row r="1102" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1102" s="1"/>
-    </row>
-    <row r="1103" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1103" s="1"/>
-    </row>
-    <row r="1104" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1104" s="1"/>
-    </row>
-    <row r="1105" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1105" s="1"/>
-    </row>
-    <row r="1106" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1106" s="1"/>
-    </row>
-    <row r="1107" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1107" s="1"/>
-    </row>
-    <row r="1108" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1108" s="1"/>
-    </row>
-    <row r="1109" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1109" s="1"/>
-    </row>
-    <row r="1110" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1110" s="1"/>
-    </row>
-    <row r="1111" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1111" s="1"/>
+      <c r="A1072" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B1072" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1072" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1072">
+        <v>4</v>
+      </c>
+      <c r="E1072">
+        <v>4</v>
+      </c>
+      <c r="F1072" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1073" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B1073" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1073" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1073">
+        <v>1</v>
+      </c>
+      <c r="E1073">
+        <v>1</v>
+      </c>
+      <c r="F1073" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1074" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B1074" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1074" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1074">
+        <v>13</v>
+      </c>
+      <c r="E1074">
+        <v>13</v>
+      </c>
+      <c r="F1074" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1075" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B1075" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1075" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1075">
+        <v>1</v>
+      </c>
+      <c r="E1075">
+        <v>1</v>
+      </c>
+      <c r="F1075" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1076" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B1076" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1076" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1076">
+        <v>4</v>
+      </c>
+      <c r="E1076">
+        <v>3</v>
+      </c>
+      <c r="F1076" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1077" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B1077" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1077" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1077">
+        <v>5</v>
+      </c>
+      <c r="E1077">
+        <v>5</v>
+      </c>
+      <c r="F1077" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1078" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B1078" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1078" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1078">
+        <v>1</v>
+      </c>
+      <c r="E1078">
+        <v>1</v>
+      </c>
+      <c r="F1078" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1079" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B1079" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1079" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1079">
+        <v>1</v>
+      </c>
+      <c r="E1079">
+        <v>1</v>
+      </c>
+      <c r="F1079" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1080" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B1080" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1080" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1080">
+        <v>15</v>
+      </c>
+      <c r="E1080">
+        <v>12</v>
+      </c>
+      <c r="F1080" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1081" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B1081" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1081" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1081">
+        <v>9</v>
+      </c>
+      <c r="E1081">
+        <v>7</v>
+      </c>
+      <c r="F1081" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1082" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B1082" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1082" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1082">
+        <v>8</v>
+      </c>
+      <c r="E1082">
+        <v>5</v>
+      </c>
+      <c r="F1082" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1083" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B1083" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1083" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1083">
+        <v>28</v>
+      </c>
+      <c r="E1083">
+        <v>27</v>
+      </c>
+      <c r="F1083" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1084" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B1084" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1084" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1084">
+        <v>4</v>
+      </c>
+      <c r="E1084">
+        <v>3</v>
+      </c>
+      <c r="F1084" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1085" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B1085" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1085" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1085">
+        <v>8</v>
+      </c>
+      <c r="E1085">
+        <v>7</v>
+      </c>
+      <c r="F1085" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1086" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B1086" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1086" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1086">
+        <v>37</v>
+      </c>
+      <c r="E1086">
+        <v>30</v>
+      </c>
+      <c r="F1086" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1087" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B1087" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1087" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1087">
+        <v>1</v>
+      </c>
+      <c r="E1087">
+        <v>1</v>
+      </c>
+      <c r="F1087" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1088" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B1088" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1088" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1088">
+        <v>8</v>
+      </c>
+      <c r="E1088">
+        <v>4</v>
+      </c>
+      <c r="F1088" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1089" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B1089" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1089" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1089">
+        <v>2</v>
+      </c>
+      <c r="E1089">
+        <v>2</v>
+      </c>
+      <c r="F1089" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1090" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B1090" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1090" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1090">
+        <v>20</v>
+      </c>
+      <c r="E1090">
+        <v>19</v>
+      </c>
+      <c r="F1090" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1091" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B1091" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1091" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1091">
+        <v>5</v>
+      </c>
+      <c r="E1091">
+        <v>3</v>
+      </c>
+      <c r="F1091" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1092" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B1092" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1092" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1092">
+        <v>7</v>
+      </c>
+      <c r="E1092">
+        <v>5</v>
+      </c>
+      <c r="F1092" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1093" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B1093" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1093" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1093">
+        <v>15</v>
+      </c>
+      <c r="E1093">
+        <v>15</v>
+      </c>
+      <c r="F1093" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1094" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B1094" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1094" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1094">
+        <v>11</v>
+      </c>
+      <c r="E1094">
+        <v>10</v>
+      </c>
+      <c r="F1094" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1095" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B1095" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1095" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1095">
+        <v>7</v>
+      </c>
+      <c r="E1095">
+        <v>6</v>
+      </c>
+      <c r="F1095" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1096" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B1096" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1096" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1096">
+        <v>11</v>
+      </c>
+      <c r="E1096">
+        <v>11</v>
+      </c>
+      <c r="F1096" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1097" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B1097" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1097" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1097">
+        <v>2</v>
+      </c>
+      <c r="E1097">
+        <v>2</v>
+      </c>
+      <c r="F1097" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1098" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B1098" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1098" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1098">
+        <v>1</v>
+      </c>
+      <c r="E1098">
+        <v>1</v>
+      </c>
+      <c r="F1098" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1099" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B1099" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1099" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1099">
+        <v>6</v>
+      </c>
+      <c r="E1099">
+        <v>6</v>
+      </c>
+      <c r="F1099" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1100" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B1100" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1100" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1100">
+        <v>5</v>
+      </c>
+      <c r="E1100">
+        <v>5</v>
+      </c>
+      <c r="F1100" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1101" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B1101" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1101" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1101">
+        <v>4</v>
+      </c>
+      <c r="E1101">
+        <v>2</v>
+      </c>
+      <c r="F1101" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1102" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B1102" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1102" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1102">
+        <v>19</v>
+      </c>
+      <c r="E1102">
+        <v>19</v>
+      </c>
+      <c r="F1102" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1103" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B1103" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1103" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1103">
+        <v>1</v>
+      </c>
+      <c r="E1103">
+        <v>1</v>
+      </c>
+      <c r="F1103" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1104" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B1104" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1104" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1104">
+        <v>30</v>
+      </c>
+      <c r="E1104">
+        <v>28</v>
+      </c>
+      <c r="F1104" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1105" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B1105" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1105" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1105">
+        <v>1</v>
+      </c>
+      <c r="E1105">
+        <v>1</v>
+      </c>
+      <c r="F1105" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1106" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B1106" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1106" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1106">
+        <v>7</v>
+      </c>
+      <c r="E1106">
+        <v>6</v>
+      </c>
+      <c r="F1106" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1107" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B1107" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1107" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1107">
+        <v>15</v>
+      </c>
+      <c r="E1107">
+        <v>15</v>
+      </c>
+      <c r="F1107" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1108" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B1108" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1108" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1108">
+        <v>2</v>
+      </c>
+      <c r="E1108">
+        <v>2</v>
+      </c>
+      <c r="F1108" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1109" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B1109" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1109" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1109">
+        <v>3</v>
+      </c>
+      <c r="E1109">
+        <v>3</v>
+      </c>
+      <c r="F1109" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1110" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B1110" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1110" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1110">
+        <v>1</v>
+      </c>
+      <c r="E1110">
+        <v>1</v>
+      </c>
+      <c r="F1110" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1111" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B1111" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1111" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1111">
+        <v>1</v>
+      </c>
+      <c r="E1111">
+        <v>1</v>
+      </c>
+      <c r="F1111" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1112" s="1">
+        <v>46193</v>
+      </c>
+      <c r="B1112" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1112" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1112">
+        <v>8</v>
+      </c>
+      <c r="E1112">
+        <v>8</v>
+      </c>
+      <c r="F1112" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1113" s="1">
+        <v>46193</v>
+      </c>
+      <c r="B1113" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1113" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1113">
+        <v>4</v>
+      </c>
+      <c r="E1113">
+        <v>4</v>
+      </c>
+      <c r="F1113" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1114" s="1">
+        <v>46193</v>
+      </c>
+      <c r="B1114" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1114" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1114">
+        <v>8</v>
+      </c>
+      <c r="E1114">
+        <v>5</v>
+      </c>
+      <c r="F1114" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1115" s="1">
+        <v>46193</v>
+      </c>
+      <c r="B1115" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1115" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1115">
+        <v>15</v>
+      </c>
+      <c r="E1115">
+        <v>14</v>
+      </c>
+      <c r="F1115" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1116" s="1">
+        <v>46193</v>
+      </c>
+      <c r="B1116" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1116" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1116">
+        <v>7</v>
+      </c>
+      <c r="E1116">
+        <v>7</v>
+      </c>
+      <c r="F1116" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1117" s="1">
+        <v>46193</v>
+      </c>
+      <c r="B1117" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1117" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1117">
+        <v>12</v>
+      </c>
+      <c r="E1117">
+        <v>6</v>
+      </c>
+      <c r="F1117" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1118" s="1">
+        <v>46193</v>
+      </c>
+      <c r="B1118" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1118" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1118">
+        <v>11</v>
+      </c>
+      <c r="E1118">
+        <v>11</v>
+      </c>
+      <c r="F1118" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1119" s="1">
+        <v>46193</v>
+      </c>
+      <c r="B1119" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1119" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1119">
+        <v>2</v>
+      </c>
+      <c r="E1119">
+        <v>2</v>
+      </c>
+      <c r="F1119" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1120" s="1">
+        <v>46193</v>
+      </c>
+      <c r="B1120" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1120" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1120">
+        <v>8</v>
+      </c>
+      <c r="E1120">
+        <v>3</v>
+      </c>
+      <c r="F1120" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1121" s="1">
+        <v>46193</v>
+      </c>
+      <c r="B1121" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1121" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1121">
+        <v>12</v>
+      </c>
+      <c r="E1121">
+        <v>10</v>
+      </c>
+      <c r="F1121" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1122" s="1">
+        <v>46193</v>
+      </c>
+      <c r="B1122" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1122" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1122">
+        <v>8</v>
+      </c>
+      <c r="E1122">
+        <v>5</v>
+      </c>
+      <c r="F1122" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1123" s="1">
+        <v>46193</v>
+      </c>
+      <c r="B1123" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1123" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1123">
+        <v>3</v>
+      </c>
+      <c r="E1123">
+        <v>1</v>
+      </c>
+      <c r="F1123" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1124" s="1">
+        <v>46193</v>
+      </c>
+      <c r="B1124" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1124" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1124">
+        <v>9</v>
+      </c>
+      <c r="E1124">
+        <v>9</v>
+      </c>
+      <c r="F1124" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1125" s="1">
+        <v>46193</v>
+      </c>
+      <c r="B1125" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1125" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1125">
+        <v>23</v>
+      </c>
+      <c r="E1125">
+        <v>23</v>
+      </c>
+      <c r="F1125" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1126" s="1">
+        <v>46193</v>
+      </c>
+      <c r="B1126" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1126" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1126">
+        <v>1</v>
+      </c>
+      <c r="E1126">
+        <v>1</v>
+      </c>
+      <c r="F1126" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1127" s="1">
+        <v>46193</v>
+      </c>
+      <c r="B1127" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1127" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1127">
+        <v>7</v>
+      </c>
+      <c r="E1127">
+        <v>6</v>
+      </c>
+      <c r="F1127" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1128" s="1">
+        <v>46193</v>
+      </c>
+      <c r="B1128" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1128" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1128">
+        <v>11</v>
+      </c>
+      <c r="E1128">
+        <v>11</v>
+      </c>
+      <c r="F1128" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1129" s="1">
+        <v>46193</v>
+      </c>
+      <c r="B1129" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1129" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1129">
+        <v>5</v>
+      </c>
+      <c r="E1129">
+        <v>3</v>
+      </c>
+      <c r="F1129" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1130" s="1">
+        <v>46193</v>
+      </c>
+      <c r="B1130" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1130" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1130">
+        <v>1</v>
+      </c>
+      <c r="E1130">
+        <v>1</v>
+      </c>
+      <c r="F1130" t="s">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1111" xr:uid="{22A7DA2E-DF85-4559-9E8B-F6EDBCD02D26}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\used_cars_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4013C78-2D74-43BA-8626-97BCAE3C12DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A158994C-0F5A-4396-98BE-9C3C5493EE67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D7CE9FC5-F49F-40D4-93B4-AA39BB343A99}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3393" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3513" uniqueCount="20">
   <si>
     <t>Date</t>
   </si>
@@ -474,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22A7DA2E-DF85-4559-9E8B-F6EDBCD02D26}">
-  <dimension ref="A1:F1130"/>
+  <dimension ref="A1:F1170"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -23082,6 +23082,806 @@
         <v>10</v>
       </c>
     </row>
+    <row r="1131" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1131" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B1131" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1131" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1131">
+        <v>13</v>
+      </c>
+      <c r="E1131">
+        <v>12</v>
+      </c>
+      <c r="F1131" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1132" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B1132" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1132" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1132">
+        <v>11</v>
+      </c>
+      <c r="E1132">
+        <v>8</v>
+      </c>
+      <c r="F1132" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1133" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B1133" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1133" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1133">
+        <v>7</v>
+      </c>
+      <c r="E1133">
+        <v>5</v>
+      </c>
+      <c r="F1133" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1134" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B1134" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1134" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1134">
+        <v>16</v>
+      </c>
+      <c r="E1134">
+        <v>15</v>
+      </c>
+      <c r="F1134" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1135" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B1135" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1135" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1135">
+        <v>17</v>
+      </c>
+      <c r="E1135">
+        <v>13</v>
+      </c>
+      <c r="F1135" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1136" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B1136" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1136" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1136">
+        <v>13</v>
+      </c>
+      <c r="E1136">
+        <v>9</v>
+      </c>
+      <c r="F1136" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1137" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B1137" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1137" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1137">
+        <v>20</v>
+      </c>
+      <c r="E1137">
+        <v>16</v>
+      </c>
+      <c r="F1137" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1138" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B1138" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1138" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1138">
+        <v>1</v>
+      </c>
+      <c r="E1138">
+        <v>1</v>
+      </c>
+      <c r="F1138" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1139" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B1139" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1139" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1139">
+        <v>4</v>
+      </c>
+      <c r="E1139">
+        <v>3</v>
+      </c>
+      <c r="F1139" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1140" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B1140" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1140" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1140">
+        <v>1</v>
+      </c>
+      <c r="E1140">
+        <v>1</v>
+      </c>
+      <c r="F1140" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1141" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B1141" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1141" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1141">
+        <v>5</v>
+      </c>
+      <c r="E1141">
+        <v>5</v>
+      </c>
+      <c r="F1141" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1142" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B1142" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1142" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1142">
+        <v>2</v>
+      </c>
+      <c r="E1142">
+        <v>2</v>
+      </c>
+      <c r="F1142" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1143" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B1143" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1143" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1143">
+        <v>6</v>
+      </c>
+      <c r="E1143">
+        <v>6</v>
+      </c>
+      <c r="F1143" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1144" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B1144" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1144" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1144">
+        <v>13</v>
+      </c>
+      <c r="E1144">
+        <v>13</v>
+      </c>
+      <c r="F1144" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1145" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B1145" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1145" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1145">
+        <v>1</v>
+      </c>
+      <c r="E1145">
+        <v>1</v>
+      </c>
+      <c r="F1145" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1146" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B1146" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1146" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1146">
+        <v>7</v>
+      </c>
+      <c r="E1146">
+        <v>7</v>
+      </c>
+      <c r="F1146" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1147" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B1147" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1147" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1147">
+        <v>1</v>
+      </c>
+      <c r="E1147">
+        <v>1</v>
+      </c>
+      <c r="F1147" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1148" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B1148" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1148" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1148">
+        <v>1</v>
+      </c>
+      <c r="E1148">
+        <v>1</v>
+      </c>
+      <c r="F1148" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1149" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B1149" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1149" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1149">
+        <v>2</v>
+      </c>
+      <c r="E1149">
+        <v>2</v>
+      </c>
+      <c r="F1149" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1150" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B1150" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1150" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1150">
+        <v>16</v>
+      </c>
+      <c r="E1150">
+        <v>16</v>
+      </c>
+      <c r="F1150" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1151" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B1151" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1151" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1151">
+        <v>6</v>
+      </c>
+      <c r="E1151">
+        <v>5</v>
+      </c>
+      <c r="F1151" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1152" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B1152" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1152" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1152">
+        <v>5</v>
+      </c>
+      <c r="E1152">
+        <v>2</v>
+      </c>
+      <c r="F1152" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1153" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B1153" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1153" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1153">
+        <v>19</v>
+      </c>
+      <c r="E1153">
+        <v>16</v>
+      </c>
+      <c r="F1153" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1154" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B1154" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1154" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1154">
+        <v>3</v>
+      </c>
+      <c r="E1154">
+        <v>3</v>
+      </c>
+      <c r="F1154" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1155" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B1155" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1155" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1155">
+        <v>5</v>
+      </c>
+      <c r="E1155">
+        <v>4</v>
+      </c>
+      <c r="F1155" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1156" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B1156" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1156" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1156">
+        <v>14</v>
+      </c>
+      <c r="E1156">
+        <v>14</v>
+      </c>
+      <c r="F1156" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1157" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B1157" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1157" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1157">
+        <v>2</v>
+      </c>
+      <c r="E1157">
+        <v>2</v>
+      </c>
+      <c r="F1157" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1158" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B1158" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1158" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1158">
+        <v>6</v>
+      </c>
+      <c r="E1158">
+        <v>3</v>
+      </c>
+      <c r="F1158" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1159" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B1159" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1159" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1159">
+        <v>8</v>
+      </c>
+      <c r="E1159">
+        <v>8</v>
+      </c>
+      <c r="F1159" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1160" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B1160" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1160" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1160">
+        <v>12</v>
+      </c>
+      <c r="E1160">
+        <v>10</v>
+      </c>
+      <c r="F1160" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1161" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B1161" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1161" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1161">
+        <v>4</v>
+      </c>
+      <c r="E1161">
+        <v>1</v>
+      </c>
+      <c r="F1161" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1162" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B1162" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1162" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1162">
+        <v>21</v>
+      </c>
+      <c r="E1162">
+        <v>19</v>
+      </c>
+      <c r="F1162" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1163" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B1163" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1163" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1163">
+        <v>1</v>
+      </c>
+      <c r="E1163">
+        <v>1</v>
+      </c>
+      <c r="F1163" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1164" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B1164" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1164" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1164">
+        <v>6</v>
+      </c>
+      <c r="E1164">
+        <v>6</v>
+      </c>
+      <c r="F1164" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1165" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B1165" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1165" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1165">
+        <v>21</v>
+      </c>
+      <c r="E1165">
+        <v>20</v>
+      </c>
+      <c r="F1165" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1166" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B1166" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1166" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1166">
+        <v>3</v>
+      </c>
+      <c r="E1166">
+        <v>3</v>
+      </c>
+      <c r="F1166" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1167" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B1167" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1167" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1167">
+        <v>4</v>
+      </c>
+      <c r="E1167">
+        <v>3</v>
+      </c>
+      <c r="F1167" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1168" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B1168" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1168" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1168">
+        <v>9</v>
+      </c>
+      <c r="E1168">
+        <v>9</v>
+      </c>
+      <c r="F1168" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1169" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B1169" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1169" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1169">
+        <v>1</v>
+      </c>
+      <c r="E1169">
+        <v>1</v>
+      </c>
+      <c r="F1169" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1170" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B1170" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1170" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1170">
+        <v>2</v>
+      </c>
+      <c r="E1170">
+        <v>1</v>
+      </c>
+      <c r="F1170" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\used_cars_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A158994C-0F5A-4396-98BE-9C3C5493EE67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6057E4A4-01F8-4363-AE14-6EE4091C1F58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D7CE9FC5-F49F-40D4-93B4-AA39BB343A99}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3513" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3564" uniqueCount="20">
   <si>
     <t>Date</t>
   </si>
@@ -474,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22A7DA2E-DF85-4559-9E8B-F6EDBCD02D26}">
-  <dimension ref="A1:F1170"/>
+  <dimension ref="A1:F1187"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -23882,6 +23882,346 @@
         <v>10</v>
       </c>
     </row>
+    <row r="1171" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1171" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B1171" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1171" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1171">
+        <v>42</v>
+      </c>
+      <c r="E1171">
+        <v>39</v>
+      </c>
+      <c r="F1171" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1172" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B1172" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1172" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1172">
+        <v>11</v>
+      </c>
+      <c r="E1172">
+        <v>10</v>
+      </c>
+      <c r="F1172" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1173" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B1173" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1173" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1173">
+        <v>13</v>
+      </c>
+      <c r="E1173">
+        <v>8</v>
+      </c>
+      <c r="F1173" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1174" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B1174" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1174" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1174">
+        <v>31</v>
+      </c>
+      <c r="E1174">
+        <v>29</v>
+      </c>
+      <c r="F1174" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1175" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B1175" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1175" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1175">
+        <v>18</v>
+      </c>
+      <c r="E1175">
+        <v>15</v>
+      </c>
+      <c r="F1175" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1176" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B1176" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1176" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1176">
+        <v>15</v>
+      </c>
+      <c r="E1176">
+        <v>11</v>
+      </c>
+      <c r="F1176" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1177" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B1177" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1177" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1177">
+        <v>7</v>
+      </c>
+      <c r="E1177">
+        <v>7</v>
+      </c>
+      <c r="F1177" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1178" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B1178" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1178" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1178">
+        <v>2</v>
+      </c>
+      <c r="E1178">
+        <v>1</v>
+      </c>
+      <c r="F1178" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1179" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B1179" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1179" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1179">
+        <v>6</v>
+      </c>
+      <c r="E1179">
+        <v>4</v>
+      </c>
+      <c r="F1179" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1180" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B1180" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1180" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1180">
+        <v>10</v>
+      </c>
+      <c r="E1180">
+        <v>9</v>
+      </c>
+      <c r="F1180" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1181" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B1181" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1181" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1181">
+        <v>3</v>
+      </c>
+      <c r="E1181">
+        <v>3</v>
+      </c>
+      <c r="F1181" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1182" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B1182" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1182" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1182">
+        <v>2</v>
+      </c>
+      <c r="E1182">
+        <v>1</v>
+      </c>
+      <c r="F1182" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1183" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B1183" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1183" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1183">
+        <v>12</v>
+      </c>
+      <c r="E1183">
+        <v>10</v>
+      </c>
+      <c r="F1183" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1184" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B1184" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1184" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1184">
+        <v>1</v>
+      </c>
+      <c r="E1184">
+        <v>1</v>
+      </c>
+      <c r="F1184" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1185" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B1185" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1185" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1185">
+        <v>22</v>
+      </c>
+      <c r="E1185">
+        <v>21</v>
+      </c>
+      <c r="F1185" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1186" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B1186" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1186" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1186">
+        <v>2</v>
+      </c>
+      <c r="E1186">
+        <v>2</v>
+      </c>
+      <c r="F1186" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1187" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B1187" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1187" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1187">
+        <v>4</v>
+      </c>
+      <c r="E1187">
+        <v>4</v>
+      </c>
+      <c r="F1187" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\used_cars_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6057E4A4-01F8-4363-AE14-6EE4091C1F58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A53391ED-2E4C-43D7-85B7-281B417B87A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D7CE9FC5-F49F-40D4-93B4-AA39BB343A99}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3564" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3615" uniqueCount="20">
   <si>
     <t>Date</t>
   </si>
@@ -474,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22A7DA2E-DF85-4559-9E8B-F6EDBCD02D26}">
-  <dimension ref="A1:F1187"/>
+  <dimension ref="A1:F1204"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -24222,6 +24222,346 @@
         <v>10</v>
       </c>
     </row>
+    <row r="1188" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1188" s="1">
+        <v>46197</v>
+      </c>
+      <c r="B1188" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1188" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1188">
+        <v>34</v>
+      </c>
+      <c r="E1188">
+        <v>32</v>
+      </c>
+      <c r="F1188" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1189" s="1">
+        <v>46197</v>
+      </c>
+      <c r="B1189" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1189" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1189">
+        <v>8</v>
+      </c>
+      <c r="E1189">
+        <v>7</v>
+      </c>
+      <c r="F1189" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1190" s="1">
+        <v>46197</v>
+      </c>
+      <c r="B1190" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1190" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1190">
+        <v>6</v>
+      </c>
+      <c r="E1190">
+        <v>6</v>
+      </c>
+      <c r="F1190" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1191" s="1">
+        <v>46197</v>
+      </c>
+      <c r="B1191" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1191" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1191">
+        <v>27</v>
+      </c>
+      <c r="E1191">
+        <v>25</v>
+      </c>
+      <c r="F1191" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1192" s="1">
+        <v>46197</v>
+      </c>
+      <c r="B1192" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1192" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1192">
+        <v>15</v>
+      </c>
+      <c r="E1192">
+        <v>13</v>
+      </c>
+      <c r="F1192" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1193" s="1">
+        <v>46197</v>
+      </c>
+      <c r="B1193" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1193" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1193">
+        <v>13</v>
+      </c>
+      <c r="E1193">
+        <v>11</v>
+      </c>
+      <c r="F1193" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1194" s="1">
+        <v>46197</v>
+      </c>
+      <c r="B1194" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1194" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1194">
+        <v>9</v>
+      </c>
+      <c r="E1194">
+        <v>9</v>
+      </c>
+      <c r="F1194" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1195" s="1">
+        <v>46197</v>
+      </c>
+      <c r="B1195" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1195" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1195">
+        <v>6</v>
+      </c>
+      <c r="E1195">
+        <v>6</v>
+      </c>
+      <c r="F1195" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1196" s="1">
+        <v>46197</v>
+      </c>
+      <c r="B1196" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1196" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1196">
+        <v>17</v>
+      </c>
+      <c r="E1196">
+        <v>16</v>
+      </c>
+      <c r="F1196" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1197" s="1">
+        <v>46197</v>
+      </c>
+      <c r="B1197" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1197" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1197">
+        <v>7</v>
+      </c>
+      <c r="E1197">
+        <v>7</v>
+      </c>
+      <c r="F1197" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1198" s="1">
+        <v>46197</v>
+      </c>
+      <c r="B1198" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1198" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1198">
+        <v>15</v>
+      </c>
+      <c r="E1198">
+        <v>15</v>
+      </c>
+      <c r="F1198" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1199" s="1">
+        <v>46197</v>
+      </c>
+      <c r="B1199" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1199" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1199">
+        <v>5</v>
+      </c>
+      <c r="E1199">
+        <v>4</v>
+      </c>
+      <c r="F1199" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1200" s="1">
+        <v>46197</v>
+      </c>
+      <c r="B1200" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1200" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1200">
+        <v>19</v>
+      </c>
+      <c r="E1200">
+        <v>18</v>
+      </c>
+      <c r="F1200" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1201" s="1">
+        <v>46197</v>
+      </c>
+      <c r="B1201" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1201" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1201">
+        <v>1</v>
+      </c>
+      <c r="E1201">
+        <v>1</v>
+      </c>
+      <c r="F1201" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1202" s="1">
+        <v>46197</v>
+      </c>
+      <c r="B1202" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1202" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1202">
+        <v>3</v>
+      </c>
+      <c r="E1202">
+        <v>3</v>
+      </c>
+      <c r="F1202" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1203" s="1">
+        <v>46197</v>
+      </c>
+      <c r="B1203" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1203" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1203">
+        <v>13</v>
+      </c>
+      <c r="E1203">
+        <v>13</v>
+      </c>
+      <c r="F1203" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1204" s="1">
+        <v>46197</v>
+      </c>
+      <c r="B1204" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1204" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1204">
+        <v>3</v>
+      </c>
+      <c r="E1204">
+        <v>2</v>
+      </c>
+      <c r="F1204" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\used_cars_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A53391ED-2E4C-43D7-85B7-281B417B87A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D7FDA18-EA58-44C0-94F5-306CEAD75829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D7CE9FC5-F49F-40D4-93B4-AA39BB343A99}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$F$1111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$F$1223</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3615" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3672" uniqueCount="20">
   <si>
     <t>Date</t>
   </si>
@@ -474,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22A7DA2E-DF85-4559-9E8B-F6EDBCD02D26}">
-  <dimension ref="A1:F1204"/>
+  <dimension ref="A1:F1223"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -24562,7 +24562,388 @@
         <v>10</v>
       </c>
     </row>
+    <row r="1205" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1205" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B1205" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1205" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1205">
+        <v>20</v>
+      </c>
+      <c r="E1205">
+        <v>19</v>
+      </c>
+      <c r="F1205" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1206" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B1206" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1206" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1206">
+        <v>6</v>
+      </c>
+      <c r="E1206">
+        <v>5</v>
+      </c>
+      <c r="F1206" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1207" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B1207" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1207" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1207">
+        <v>10</v>
+      </c>
+      <c r="E1207">
+        <v>7</v>
+      </c>
+      <c r="F1207" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1208" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B1208" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1208" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1208">
+        <v>33</v>
+      </c>
+      <c r="E1208">
+        <v>29</v>
+      </c>
+      <c r="F1208" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1209" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B1209" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1209" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1209">
+        <v>17</v>
+      </c>
+      <c r="E1209">
+        <v>14</v>
+      </c>
+      <c r="F1209" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1210" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B1210" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1210" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1210">
+        <v>14</v>
+      </c>
+      <c r="E1210">
+        <v>10</v>
+      </c>
+      <c r="F1210" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1211" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B1211" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1211" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1211">
+        <v>13</v>
+      </c>
+      <c r="E1211">
+        <v>13</v>
+      </c>
+      <c r="F1211" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1212" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B1212" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1212" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1212">
+        <v>5</v>
+      </c>
+      <c r="E1212">
+        <v>3</v>
+      </c>
+      <c r="F1212" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1213" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B1213" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1213" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1213">
+        <v>1</v>
+      </c>
+      <c r="E1213">
+        <v>1</v>
+      </c>
+      <c r="F1213" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1214" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B1214" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1214" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1214">
+        <v>15</v>
+      </c>
+      <c r="E1214">
+        <v>14</v>
+      </c>
+      <c r="F1214" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1215" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B1215" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1215" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1215">
+        <v>8</v>
+      </c>
+      <c r="E1215">
+        <v>8</v>
+      </c>
+      <c r="F1215" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1216" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B1216" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1216" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1216">
+        <v>10</v>
+      </c>
+      <c r="E1216">
+        <v>5</v>
+      </c>
+      <c r="F1216" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1217" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B1217" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1217" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1217">
+        <v>18</v>
+      </c>
+      <c r="E1217">
+        <v>16</v>
+      </c>
+      <c r="F1217" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1218" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B1218" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1218" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1218">
+        <v>5</v>
+      </c>
+      <c r="E1218">
+        <v>3</v>
+      </c>
+      <c r="F1218" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1219" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B1219" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1219" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1219">
+        <v>23</v>
+      </c>
+      <c r="E1219">
+        <v>20</v>
+      </c>
+      <c r="F1219" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1220" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B1220" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1220" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1220">
+        <v>4</v>
+      </c>
+      <c r="E1220">
+        <v>4</v>
+      </c>
+      <c r="F1220" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1221" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B1221" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1221" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1221">
+        <v>3</v>
+      </c>
+      <c r="E1221">
+        <v>2</v>
+      </c>
+      <c r="F1221" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1222" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B1222" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1222" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1222">
+        <v>8</v>
+      </c>
+      <c r="E1222">
+        <v>8</v>
+      </c>
+      <c r="F1222" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1223" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B1223" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1223" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1223">
+        <v>6</v>
+      </c>
+      <c r="E1223">
+        <v>4</v>
+      </c>
+      <c r="F1223" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:F1223" xr:uid="{22A7DA2E-DF85-4559-9E8B-F6EDBCD02D26}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\used_cars_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D7FDA18-EA58-44C0-94F5-306CEAD75829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76BB3CF7-3A59-4622-BE58-8B2686F0B26D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D7CE9FC5-F49F-40D4-93B4-AA39BB343A99}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3672" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3828" uniqueCount="20">
   <si>
     <t>Date</t>
   </si>
@@ -474,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22A7DA2E-DF85-4559-9E8B-F6EDBCD02D26}">
-  <dimension ref="A1:F1223"/>
+  <dimension ref="A1:F1275"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -24942,6 +24942,1046 @@
         <v>10</v>
       </c>
     </row>
+    <row r="1224" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1224" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B1224" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1224" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1224">
+        <v>30</v>
+      </c>
+      <c r="E1224">
+        <v>27</v>
+      </c>
+      <c r="F1224" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1225" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B1225" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1225" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1225">
+        <v>17</v>
+      </c>
+      <c r="E1225">
+        <v>15</v>
+      </c>
+      <c r="F1225" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1226" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B1226" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1226" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1226">
+        <v>19</v>
+      </c>
+      <c r="E1226">
+        <v>10</v>
+      </c>
+      <c r="F1226" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1227" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B1227" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1227" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1227">
+        <v>38</v>
+      </c>
+      <c r="E1227">
+        <v>37</v>
+      </c>
+      <c r="F1227" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1228" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B1228" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1228" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1228">
+        <v>10</v>
+      </c>
+      <c r="E1228">
+        <v>10</v>
+      </c>
+      <c r="F1228" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1229" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B1229" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1229" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1229">
+        <v>19</v>
+      </c>
+      <c r="E1229">
+        <v>15</v>
+      </c>
+      <c r="F1229" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1230" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B1230" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1230" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1230">
+        <v>5</v>
+      </c>
+      <c r="E1230">
+        <v>5</v>
+      </c>
+      <c r="F1230" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1231" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B1231" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1231" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1231">
+        <v>1</v>
+      </c>
+      <c r="E1231">
+        <v>1</v>
+      </c>
+      <c r="F1231" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1232" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B1232" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1232" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1232">
+        <v>9</v>
+      </c>
+      <c r="E1232">
+        <v>7</v>
+      </c>
+      <c r="F1232" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1233" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B1233" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1233" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1233">
+        <v>17</v>
+      </c>
+      <c r="E1233">
+        <v>15</v>
+      </c>
+      <c r="F1233" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1234" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B1234" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1234" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1234">
+        <v>4</v>
+      </c>
+      <c r="E1234">
+        <v>4</v>
+      </c>
+      <c r="F1234" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1235" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B1235" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1235" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1235">
+        <v>7</v>
+      </c>
+      <c r="E1235">
+        <v>3</v>
+      </c>
+      <c r="F1235" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1236" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B1236" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1236" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1236">
+        <v>7</v>
+      </c>
+      <c r="E1236">
+        <v>7</v>
+      </c>
+      <c r="F1236" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1237" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B1237" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1237" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1237">
+        <v>6</v>
+      </c>
+      <c r="E1237">
+        <v>5</v>
+      </c>
+      <c r="F1237" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1238" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B1238" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1238" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1238">
+        <v>2</v>
+      </c>
+      <c r="E1238">
+        <v>2</v>
+      </c>
+      <c r="F1238" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1239" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B1239" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1239" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1239">
+        <v>16</v>
+      </c>
+      <c r="E1239">
+        <v>15</v>
+      </c>
+      <c r="F1239" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1240" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B1240" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1240" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1240">
+        <v>4</v>
+      </c>
+      <c r="E1240">
+        <v>4</v>
+      </c>
+      <c r="F1240" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1241" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B1241" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1241" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1241">
+        <v>3</v>
+      </c>
+      <c r="E1241">
+        <v>3</v>
+      </c>
+      <c r="F1241" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1242" s="1">
+        <v>46200</v>
+      </c>
+      <c r="B1242" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1242" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1242">
+        <v>28</v>
+      </c>
+      <c r="E1242">
+        <v>24</v>
+      </c>
+      <c r="F1242" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1243" s="1">
+        <v>46200</v>
+      </c>
+      <c r="B1243" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1243" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1243">
+        <v>5</v>
+      </c>
+      <c r="E1243">
+        <v>5</v>
+      </c>
+      <c r="F1243" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1244" s="1">
+        <v>46200</v>
+      </c>
+      <c r="B1244" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1244" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1244">
+        <v>8</v>
+      </c>
+      <c r="E1244">
+        <v>7</v>
+      </c>
+      <c r="F1244" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1245" s="1">
+        <v>46200</v>
+      </c>
+      <c r="B1245" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1245" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1245">
+        <v>59</v>
+      </c>
+      <c r="E1245">
+        <v>52</v>
+      </c>
+      <c r="F1245" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1246" s="1">
+        <v>46200</v>
+      </c>
+      <c r="B1246" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1246" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1246">
+        <v>16</v>
+      </c>
+      <c r="E1246">
+        <v>14</v>
+      </c>
+      <c r="F1246" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1247" s="1">
+        <v>46200</v>
+      </c>
+      <c r="B1247" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1247" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1247">
+        <v>16</v>
+      </c>
+      <c r="E1247">
+        <v>13</v>
+      </c>
+      <c r="F1247" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1248" s="1">
+        <v>46200</v>
+      </c>
+      <c r="B1248" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1248" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1248">
+        <v>14</v>
+      </c>
+      <c r="E1248">
+        <v>11</v>
+      </c>
+      <c r="F1248" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1249" s="1">
+        <v>46200</v>
+      </c>
+      <c r="B1249" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1249" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1249">
+        <v>2</v>
+      </c>
+      <c r="E1249">
+        <v>2</v>
+      </c>
+      <c r="F1249" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1250" s="1">
+        <v>46200</v>
+      </c>
+      <c r="B1250" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1250" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1250">
+        <v>5</v>
+      </c>
+      <c r="E1250">
+        <v>3</v>
+      </c>
+      <c r="F1250" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1251" s="1">
+        <v>46200</v>
+      </c>
+      <c r="B1251" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1251" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1251">
+        <v>41</v>
+      </c>
+      <c r="E1251">
+        <v>33</v>
+      </c>
+      <c r="F1251" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1252" s="1">
+        <v>46200</v>
+      </c>
+      <c r="B1252" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1252" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1252">
+        <v>5</v>
+      </c>
+      <c r="E1252">
+        <v>5</v>
+      </c>
+      <c r="F1252" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1253" s="1">
+        <v>46200</v>
+      </c>
+      <c r="B1253" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1253" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1253">
+        <v>10</v>
+      </c>
+      <c r="E1253">
+        <v>8</v>
+      </c>
+      <c r="F1253" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1254" s="1">
+        <v>46200</v>
+      </c>
+      <c r="B1254" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1254" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1254">
+        <v>22</v>
+      </c>
+      <c r="E1254">
+        <v>21</v>
+      </c>
+      <c r="F1254" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1255" s="1">
+        <v>46200</v>
+      </c>
+      <c r="B1255" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1255" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1255">
+        <v>3</v>
+      </c>
+      <c r="E1255">
+        <v>2</v>
+      </c>
+      <c r="F1255" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1256" s="1">
+        <v>46200</v>
+      </c>
+      <c r="B1256" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1256" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1256">
+        <v>12</v>
+      </c>
+      <c r="E1256">
+        <v>8</v>
+      </c>
+      <c r="F1256" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1257" s="1">
+        <v>46200</v>
+      </c>
+      <c r="B1257" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1257" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1257">
+        <v>1</v>
+      </c>
+      <c r="E1257">
+        <v>1</v>
+      </c>
+      <c r="F1257" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1258" s="1">
+        <v>46200</v>
+      </c>
+      <c r="B1258" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1258" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1258">
+        <v>3</v>
+      </c>
+      <c r="E1258">
+        <v>3</v>
+      </c>
+      <c r="F1258" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1259" s="1">
+        <v>46201</v>
+      </c>
+      <c r="B1259" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1259" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1259">
+        <v>32</v>
+      </c>
+      <c r="E1259">
+        <v>30</v>
+      </c>
+      <c r="F1259" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1260" s="1">
+        <v>46201</v>
+      </c>
+      <c r="B1260" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1260" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1260">
+        <v>24</v>
+      </c>
+      <c r="E1260">
+        <v>20</v>
+      </c>
+      <c r="F1260" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1261" s="1">
+        <v>46201</v>
+      </c>
+      <c r="B1261" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1261" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1261">
+        <v>15</v>
+      </c>
+      <c r="E1261">
+        <v>10</v>
+      </c>
+      <c r="F1261" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1262" s="1">
+        <v>46201</v>
+      </c>
+      <c r="B1262" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1262" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1262">
+        <v>53</v>
+      </c>
+      <c r="E1262">
+        <v>49</v>
+      </c>
+      <c r="F1262" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1263" s="1">
+        <v>46201</v>
+      </c>
+      <c r="B1263" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1263" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1263">
+        <v>15</v>
+      </c>
+      <c r="E1263">
+        <v>14</v>
+      </c>
+      <c r="F1263" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1264" s="1">
+        <v>46201</v>
+      </c>
+      <c r="B1264" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1264" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1264">
+        <v>22</v>
+      </c>
+      <c r="E1264">
+        <v>19</v>
+      </c>
+      <c r="F1264" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1265" s="1">
+        <v>46201</v>
+      </c>
+      <c r="B1265" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1265" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1265">
+        <v>16</v>
+      </c>
+      <c r="E1265">
+        <v>15</v>
+      </c>
+      <c r="F1265" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1266" s="1">
+        <v>46201</v>
+      </c>
+      <c r="B1266" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1266" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1266">
+        <v>8</v>
+      </c>
+      <c r="E1266">
+        <v>7</v>
+      </c>
+      <c r="F1266" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1267" s="1">
+        <v>46201</v>
+      </c>
+      <c r="B1267" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1267" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1267">
+        <v>7</v>
+      </c>
+      <c r="E1267">
+        <v>3</v>
+      </c>
+      <c r="F1267" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1268" s="1">
+        <v>46201</v>
+      </c>
+      <c r="B1268" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1268" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1268">
+        <v>28</v>
+      </c>
+      <c r="E1268">
+        <v>28</v>
+      </c>
+      <c r="F1268" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1269" s="1">
+        <v>46201</v>
+      </c>
+      <c r="B1269" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1269" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1269">
+        <v>1</v>
+      </c>
+      <c r="E1269">
+        <v>1</v>
+      </c>
+      <c r="F1269" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1270" s="1">
+        <v>46201</v>
+      </c>
+      <c r="B1270" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1270" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1270">
+        <v>3</v>
+      </c>
+      <c r="E1270">
+        <v>3</v>
+      </c>
+      <c r="F1270" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1271" s="1">
+        <v>46201</v>
+      </c>
+      <c r="B1271" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1271" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1271">
+        <v>41</v>
+      </c>
+      <c r="E1271">
+        <v>39</v>
+      </c>
+      <c r="F1271" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1272" s="1">
+        <v>46201</v>
+      </c>
+      <c r="B1272" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1272" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1272">
+        <v>3</v>
+      </c>
+      <c r="E1272">
+        <v>2</v>
+      </c>
+      <c r="F1272" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1273" s="1">
+        <v>46201</v>
+      </c>
+      <c r="B1273" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1273" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1273">
+        <v>11</v>
+      </c>
+      <c r="E1273">
+        <v>11</v>
+      </c>
+      <c r="F1273" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1274" s="1">
+        <v>46201</v>
+      </c>
+      <c r="B1274" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1274" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1274">
+        <v>2</v>
+      </c>
+      <c r="E1274">
+        <v>2</v>
+      </c>
+      <c r="F1274" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1275" s="1">
+        <v>46201</v>
+      </c>
+      <c r="B1275" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1275" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1275">
+        <v>4</v>
+      </c>
+      <c r="E1275">
+        <v>4</v>
+      </c>
+      <c r="F1275" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1223" xr:uid="{22A7DA2E-DF85-4559-9E8B-F6EDBCD02D26}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\used_cars_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76BB3CF7-3A59-4622-BE58-8B2686F0B26D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3EFC9EA-2562-4868-BB9C-5871250E9436}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D7CE9FC5-F49F-40D4-93B4-AA39BB343A99}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3828" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3933" uniqueCount="20">
   <si>
     <t>Date</t>
   </si>
@@ -474,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22A7DA2E-DF85-4559-9E8B-F6EDBCD02D26}">
-  <dimension ref="A1:F1275"/>
+  <dimension ref="A1:F1310"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -25982,6 +25982,706 @@
         <v>10</v>
       </c>
     </row>
+    <row r="1276" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1276" s="1">
+        <v>46202</v>
+      </c>
+      <c r="B1276" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1276" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1276">
+        <v>28</v>
+      </c>
+      <c r="E1276">
+        <v>25</v>
+      </c>
+      <c r="F1276" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1277" s="1">
+        <v>46202</v>
+      </c>
+      <c r="B1277" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1277" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1277">
+        <v>11</v>
+      </c>
+      <c r="E1277">
+        <v>10</v>
+      </c>
+      <c r="F1277" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1278" s="1">
+        <v>46202</v>
+      </c>
+      <c r="B1278" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1278" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1278">
+        <v>14</v>
+      </c>
+      <c r="E1278">
+        <v>10</v>
+      </c>
+      <c r="F1278" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1279" s="1">
+        <v>46202</v>
+      </c>
+      <c r="B1279" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1279" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1279">
+        <v>32</v>
+      </c>
+      <c r="E1279">
+        <v>29</v>
+      </c>
+      <c r="F1279" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1280" s="1">
+        <v>46202</v>
+      </c>
+      <c r="B1280" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1280" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1280">
+        <v>10</v>
+      </c>
+      <c r="E1280">
+        <v>8</v>
+      </c>
+      <c r="F1280" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1281" s="1">
+        <v>46202</v>
+      </c>
+      <c r="B1281" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1281" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1281">
+        <v>12</v>
+      </c>
+      <c r="E1281">
+        <v>9</v>
+      </c>
+      <c r="F1281" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1282" s="1">
+        <v>46202</v>
+      </c>
+      <c r="B1282" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1282" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1282">
+        <v>7</v>
+      </c>
+      <c r="E1282">
+        <v>6</v>
+      </c>
+      <c r="F1282" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1283" s="1">
+        <v>46202</v>
+      </c>
+      <c r="B1283" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1283" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1283">
+        <v>1</v>
+      </c>
+      <c r="E1283">
+        <v>1</v>
+      </c>
+      <c r="F1283" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1284" s="1">
+        <v>46202</v>
+      </c>
+      <c r="B1284" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1284" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1284">
+        <v>2</v>
+      </c>
+      <c r="E1284">
+        <v>2</v>
+      </c>
+      <c r="F1284" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1285" s="1">
+        <v>46202</v>
+      </c>
+      <c r="B1285" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1285" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1285">
+        <v>32</v>
+      </c>
+      <c r="E1285">
+        <v>26</v>
+      </c>
+      <c r="F1285" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1286" s="1">
+        <v>46202</v>
+      </c>
+      <c r="B1286" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1286" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1286">
+        <v>4</v>
+      </c>
+      <c r="E1286">
+        <v>4</v>
+      </c>
+      <c r="F1286" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1287" s="1">
+        <v>46202</v>
+      </c>
+      <c r="B1287" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1287" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1287">
+        <v>8</v>
+      </c>
+      <c r="E1287">
+        <v>4</v>
+      </c>
+      <c r="F1287" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1288" s="1">
+        <v>46202</v>
+      </c>
+      <c r="B1288" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1288" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1288">
+        <v>12</v>
+      </c>
+      <c r="E1288">
+        <v>12</v>
+      </c>
+      <c r="F1288" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1289" s="1">
+        <v>46202</v>
+      </c>
+      <c r="B1289" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1289" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1289">
+        <v>3</v>
+      </c>
+      <c r="E1289">
+        <v>3</v>
+      </c>
+      <c r="F1289" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1290" s="1">
+        <v>46202</v>
+      </c>
+      <c r="B1290" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1290" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1290">
+        <v>6</v>
+      </c>
+      <c r="E1290">
+        <v>6</v>
+      </c>
+      <c r="F1290" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1291" s="1">
+        <v>46202</v>
+      </c>
+      <c r="B1291" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1291" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1291">
+        <v>4</v>
+      </c>
+      <c r="E1291">
+        <v>3</v>
+      </c>
+      <c r="F1291" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1292" s="1">
+        <v>46202</v>
+      </c>
+      <c r="B1292" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1292" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1292">
+        <v>12</v>
+      </c>
+      <c r="E1292">
+        <v>12</v>
+      </c>
+      <c r="F1292" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1293" s="1">
+        <v>46202</v>
+      </c>
+      <c r="B1293" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1293" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1293">
+        <v>1</v>
+      </c>
+      <c r="E1293">
+        <v>1</v>
+      </c>
+      <c r="F1293" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1294" s="1">
+        <v>46202</v>
+      </c>
+      <c r="B1294" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1294" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1294">
+        <v>4</v>
+      </c>
+      <c r="E1294">
+        <v>2</v>
+      </c>
+      <c r="F1294" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1295" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B1295" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1295" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1295">
+        <v>23</v>
+      </c>
+      <c r="E1295">
+        <v>23</v>
+      </c>
+      <c r="F1295" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1296" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B1296" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1296" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1296">
+        <v>12</v>
+      </c>
+      <c r="E1296">
+        <v>12</v>
+      </c>
+      <c r="F1296" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1297" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B1297" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1297" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1297">
+        <v>12</v>
+      </c>
+      <c r="E1297">
+        <v>11</v>
+      </c>
+      <c r="F1297" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1298" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B1298" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1298" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1298">
+        <v>28</v>
+      </c>
+      <c r="E1298">
+        <v>27</v>
+      </c>
+      <c r="F1298" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1299" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B1299" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1299" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1299">
+        <v>6</v>
+      </c>
+      <c r="E1299">
+        <v>6</v>
+      </c>
+      <c r="F1299" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1300" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B1300" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1300" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1300">
+        <v>6</v>
+      </c>
+      <c r="E1300">
+        <v>5</v>
+      </c>
+      <c r="F1300" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1301" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B1301" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1301" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1301">
+        <v>2</v>
+      </c>
+      <c r="E1301">
+        <v>2</v>
+      </c>
+      <c r="F1301" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1302" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B1302" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1302" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1302">
+        <v>14</v>
+      </c>
+      <c r="E1302">
+        <v>13</v>
+      </c>
+      <c r="F1302" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1303" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B1303" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1303" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1303">
+        <v>7</v>
+      </c>
+      <c r="E1303">
+        <v>6</v>
+      </c>
+      <c r="F1303" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1304" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B1304" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1304" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1304">
+        <v>4</v>
+      </c>
+      <c r="E1304">
+        <v>2</v>
+      </c>
+      <c r="F1304" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1305" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B1305" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1305" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1305">
+        <v>7</v>
+      </c>
+      <c r="E1305">
+        <v>7</v>
+      </c>
+      <c r="F1305" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1306" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B1306" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1306" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1306">
+        <v>4</v>
+      </c>
+      <c r="E1306">
+        <v>3</v>
+      </c>
+      <c r="F1306" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1307" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B1307" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1307" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1307">
+        <v>9</v>
+      </c>
+      <c r="E1307">
+        <v>9</v>
+      </c>
+      <c r="F1307" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1308" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B1308" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1308" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1308">
+        <v>1</v>
+      </c>
+      <c r="E1308">
+        <v>1</v>
+      </c>
+      <c r="F1308" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1309" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B1309" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1309" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1309">
+        <v>6</v>
+      </c>
+      <c r="E1309">
+        <v>3</v>
+      </c>
+      <c r="F1309" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1310" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B1310" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1310" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1310">
+        <v>2</v>
+      </c>
+      <c r="E1310">
+        <v>1</v>
+      </c>
+      <c r="F1310" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1223" xr:uid="{22A7DA2E-DF85-4559-9E8B-F6EDBCD02D26}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\used_cars_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3EFC9EA-2562-4868-BB9C-5871250E9436}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25649A55-658E-4157-A260-40DA275AF4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D7CE9FC5-F49F-40D4-93B4-AA39BB343A99}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3933" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3990" uniqueCount="20">
   <si>
     <t>Date</t>
   </si>
@@ -474,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22A7DA2E-DF85-4559-9E8B-F6EDBCD02D26}">
-  <dimension ref="A1:F1310"/>
+  <dimension ref="A1:F1329"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -26682,8 +26682,389 @@
         <v>10</v>
       </c>
     </row>
+    <row r="1311" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1311" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B1311" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1311" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1311">
+        <v>18</v>
+      </c>
+      <c r="E1311">
+        <v>18</v>
+      </c>
+      <c r="F1311" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1312" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B1312" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1312" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1312">
+        <v>5</v>
+      </c>
+      <c r="E1312">
+        <v>5</v>
+      </c>
+      <c r="F1312" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1313" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B1313" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1313" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1313">
+        <v>8</v>
+      </c>
+      <c r="E1313">
+        <v>7</v>
+      </c>
+      <c r="F1313" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1314" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B1314" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1314" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1314">
+        <v>38</v>
+      </c>
+      <c r="E1314">
+        <v>35</v>
+      </c>
+      <c r="F1314" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1315" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B1315" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1315" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1315">
+        <v>4</v>
+      </c>
+      <c r="E1315">
+        <v>4</v>
+      </c>
+      <c r="F1315" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1316" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B1316" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1316" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1316">
+        <v>8</v>
+      </c>
+      <c r="E1316">
+        <v>6</v>
+      </c>
+      <c r="F1316" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1317" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B1317" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1317" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1317">
+        <v>7</v>
+      </c>
+      <c r="E1317">
+        <v>7</v>
+      </c>
+      <c r="F1317" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1318" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B1318" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1318" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1318">
+        <v>2</v>
+      </c>
+      <c r="E1318">
+        <v>2</v>
+      </c>
+      <c r="F1318" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1319" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B1319" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1319" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1319">
+        <v>2</v>
+      </c>
+      <c r="E1319">
+        <v>1</v>
+      </c>
+      <c r="F1319" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1320" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B1320" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1320" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1320">
+        <v>11</v>
+      </c>
+      <c r="E1320">
+        <v>8</v>
+      </c>
+      <c r="F1320" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1321" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B1321" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1321" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1321">
+        <v>6</v>
+      </c>
+      <c r="E1321">
+        <v>6</v>
+      </c>
+      <c r="F1321" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1322" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B1322" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1322" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1322">
+        <v>8</v>
+      </c>
+      <c r="E1322">
+        <v>5</v>
+      </c>
+      <c r="F1322" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1323" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B1323" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1323" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1323">
+        <v>1</v>
+      </c>
+      <c r="E1323">
+        <v>1</v>
+      </c>
+      <c r="F1323" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1324" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B1324" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1324" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1324">
+        <v>2</v>
+      </c>
+      <c r="E1324">
+        <v>2</v>
+      </c>
+      <c r="F1324" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1325" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B1325" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1325" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1325">
+        <v>1</v>
+      </c>
+      <c r="E1325">
+        <v>1</v>
+      </c>
+      <c r="F1325" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1326" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B1326" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1326" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1326">
+        <v>9</v>
+      </c>
+      <c r="E1326">
+        <v>9</v>
+      </c>
+      <c r="F1326" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1327" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B1327" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1327" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1327">
+        <v>1</v>
+      </c>
+      <c r="E1327">
+        <v>1</v>
+      </c>
+      <c r="F1327" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1328" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B1328" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1328" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1328">
+        <v>11</v>
+      </c>
+      <c r="E1328">
+        <v>11</v>
+      </c>
+      <c r="F1328" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1329" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B1329" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1329" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1329">
+        <v>3</v>
+      </c>
+      <c r="E1329">
+        <v>3</v>
+      </c>
+      <c r="F1329" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1223" xr:uid="{22A7DA2E-DF85-4559-9E8B-F6EDBCD02D26}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\used_cars_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25649A55-658E-4157-A260-40DA275AF4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{860E52C9-5126-4CD2-94FA-973FAD9C998F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D7CE9FC5-F49F-40D4-93B4-AA39BB343A99}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3990" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4044" uniqueCount="20">
   <si>
     <t>Date</t>
   </si>
@@ -474,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22A7DA2E-DF85-4559-9E8B-F6EDBCD02D26}">
-  <dimension ref="A1:F1329"/>
+  <dimension ref="A1:F1347"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -27062,6 +27062,366 @@
         <v>10</v>
       </c>
     </row>
+    <row r="1330" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1330" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B1330" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1330" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1330">
+        <v>13</v>
+      </c>
+      <c r="E1330">
+        <v>13</v>
+      </c>
+      <c r="F1330" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1331" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B1331" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1331" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1331">
+        <v>7</v>
+      </c>
+      <c r="E1331">
+        <v>6</v>
+      </c>
+      <c r="F1331" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1332" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B1332" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1332" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1332">
+        <v>9</v>
+      </c>
+      <c r="E1332">
+        <v>6</v>
+      </c>
+      <c r="F1332" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1333" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B1333" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1333" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1333">
+        <v>42</v>
+      </c>
+      <c r="E1333">
+        <v>33</v>
+      </c>
+      <c r="F1333" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1334" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B1334" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1334" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1334">
+        <v>12</v>
+      </c>
+      <c r="E1334">
+        <v>12</v>
+      </c>
+      <c r="F1334" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1335" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B1335" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1335" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1335">
+        <v>14</v>
+      </c>
+      <c r="E1335">
+        <v>10</v>
+      </c>
+      <c r="F1335" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1336" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B1336" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1336" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1336">
+        <v>5</v>
+      </c>
+      <c r="E1336">
+        <v>5</v>
+      </c>
+      <c r="F1336" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1337" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B1337" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1337" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1337">
+        <v>2</v>
+      </c>
+      <c r="E1337">
+        <v>2</v>
+      </c>
+      <c r="F1337" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1338" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1338" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B1338" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1338" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1338">
+        <v>12</v>
+      </c>
+      <c r="E1338">
+        <v>11</v>
+      </c>
+      <c r="F1338" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1339" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B1339" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1339" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1339">
+        <v>6</v>
+      </c>
+      <c r="E1339">
+        <v>6</v>
+      </c>
+      <c r="F1339" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1340" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B1340" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1340" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1340">
+        <v>8</v>
+      </c>
+      <c r="E1340">
+        <v>4</v>
+      </c>
+      <c r="F1340" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1341" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1341" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B1341" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1341" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1341">
+        <v>5</v>
+      </c>
+      <c r="E1341">
+        <v>4</v>
+      </c>
+      <c r="F1341" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1342" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B1342" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1342" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1342">
+        <v>13</v>
+      </c>
+      <c r="E1342">
+        <v>13</v>
+      </c>
+      <c r="F1342" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1343" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B1343" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1343" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1343">
+        <v>1</v>
+      </c>
+      <c r="E1343">
+        <v>1</v>
+      </c>
+      <c r="F1343" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1344" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1344" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B1344" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1344" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1344">
+        <v>1</v>
+      </c>
+      <c r="E1344">
+        <v>1</v>
+      </c>
+      <c r="F1344" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1345" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1345" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B1345" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1345" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1345">
+        <v>14</v>
+      </c>
+      <c r="E1345">
+        <v>13</v>
+      </c>
+      <c r="F1345" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1346" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B1346" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1346" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1346">
+        <v>1</v>
+      </c>
+      <c r="E1346">
+        <v>1</v>
+      </c>
+      <c r="F1346" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1347" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1347" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B1347" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1347" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1347">
+        <v>2</v>
+      </c>
+      <c r="E1347">
+        <v>1</v>
+      </c>
+      <c r="F1347" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1223" xr:uid="{22A7DA2E-DF85-4559-9E8B-F6EDBCD02D26}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\used_cars_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{860E52C9-5126-4CD2-94FA-973FAD9C998F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1E5EA70-E199-4C35-8A68-26EF199DE57B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D7CE9FC5-F49F-40D4-93B4-AA39BB343A99}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4044" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4098" uniqueCount="21">
   <si>
     <t>Date</t>
   </si>
@@ -102,6 +102,9 @@
   </si>
   <si>
     <t>UC-DSA-Nashik-UsedCars</t>
+  </si>
+  <si>
+    <t>Demand-Gen-Nashik-1july-UC</t>
   </si>
 </sst>
 </file>
@@ -474,7 +477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22A7DA2E-DF85-4559-9E8B-F6EDBCD02D26}">
-  <dimension ref="A1:F1347"/>
+  <dimension ref="A1:F1365"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -27422,6 +27425,366 @@
         <v>10</v>
       </c>
     </row>
+    <row r="1348" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1348" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B1348" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1348" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1348">
+        <v>9</v>
+      </c>
+      <c r="E1348">
+        <v>9</v>
+      </c>
+      <c r="F1348" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1349" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B1349" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1349" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1349">
+        <v>10</v>
+      </c>
+      <c r="E1349">
+        <v>8</v>
+      </c>
+      <c r="F1349" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1350" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B1350" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1350" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1350">
+        <v>2</v>
+      </c>
+      <c r="E1350">
+        <v>2</v>
+      </c>
+      <c r="F1350" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1351" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B1351" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1351" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1351">
+        <v>37</v>
+      </c>
+      <c r="E1351">
+        <v>33</v>
+      </c>
+      <c r="F1351" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1352" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B1352" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1352" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1352">
+        <v>12</v>
+      </c>
+      <c r="E1352">
+        <v>11</v>
+      </c>
+      <c r="F1352" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1353" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B1353" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1353" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1353">
+        <v>10</v>
+      </c>
+      <c r="E1353">
+        <v>6</v>
+      </c>
+      <c r="F1353" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1354" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1354" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B1354" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1354" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1354">
+        <v>6</v>
+      </c>
+      <c r="E1354">
+        <v>6</v>
+      </c>
+      <c r="F1354" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1355" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B1355" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1355" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1355">
+        <v>1</v>
+      </c>
+      <c r="E1355">
+        <v>1</v>
+      </c>
+      <c r="F1355" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1356" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B1356" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1356" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1356">
+        <v>1</v>
+      </c>
+      <c r="E1356">
+        <v>1</v>
+      </c>
+      <c r="F1356" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1357" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B1357" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1357" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1357">
+        <v>9</v>
+      </c>
+      <c r="E1357">
+        <v>9</v>
+      </c>
+      <c r="F1357" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1358" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B1358" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1358" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1358">
+        <v>1</v>
+      </c>
+      <c r="E1358">
+        <v>1</v>
+      </c>
+      <c r="F1358" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1359" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1359" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B1359" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1359" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1359">
+        <v>4</v>
+      </c>
+      <c r="E1359">
+        <v>3</v>
+      </c>
+      <c r="F1359" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1360" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1360" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B1360" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1360" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1360">
+        <v>2</v>
+      </c>
+      <c r="E1360">
+        <v>2</v>
+      </c>
+      <c r="F1360" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1361" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B1361" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1361" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1361">
+        <v>24</v>
+      </c>
+      <c r="E1361">
+        <v>19</v>
+      </c>
+      <c r="F1361" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1362" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B1362" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1362" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1362">
+        <v>2</v>
+      </c>
+      <c r="E1362">
+        <v>2</v>
+      </c>
+      <c r="F1362" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1363" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B1363" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1363" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1363">
+        <v>2</v>
+      </c>
+      <c r="E1363">
+        <v>2</v>
+      </c>
+      <c r="F1363" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1364" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B1364" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1364" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1364">
+        <v>4</v>
+      </c>
+      <c r="E1364">
+        <v>4</v>
+      </c>
+      <c r="F1364" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1365" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B1365" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1365" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1365">
+        <v>5</v>
+      </c>
+      <c r="E1365">
+        <v>4</v>
+      </c>
+      <c r="F1365" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1223" xr:uid="{22A7DA2E-DF85-4559-9E8B-F6EDBCD02D26}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\used_cars_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1E5EA70-E199-4C35-8A68-26EF199DE57B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7576E54E-07EF-4776-98A0-45176192C974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D7CE9FC5-F49F-40D4-93B4-AA39BB343A99}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4098" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4149" uniqueCount="21">
   <si>
     <t>Date</t>
   </si>
@@ -477,7 +477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22A7DA2E-DF85-4559-9E8B-F6EDBCD02D26}">
-  <dimension ref="A1:F1365"/>
+  <dimension ref="A1:F1382"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -27785,6 +27785,346 @@
         <v>10</v>
       </c>
     </row>
+    <row r="1366" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1366" s="1">
+        <v>46207</v>
+      </c>
+      <c r="B1366" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1366" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1366">
+        <v>15</v>
+      </c>
+      <c r="E1366">
+        <v>15</v>
+      </c>
+      <c r="F1366" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1367" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1367" s="1">
+        <v>46207</v>
+      </c>
+      <c r="B1367" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1367" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1367">
+        <v>9</v>
+      </c>
+      <c r="E1367">
+        <v>8</v>
+      </c>
+      <c r="F1367" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1368" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1368" s="1">
+        <v>46207</v>
+      </c>
+      <c r="B1368" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1368" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1368">
+        <v>5</v>
+      </c>
+      <c r="E1368">
+        <v>5</v>
+      </c>
+      <c r="F1368" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1369" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1369" s="1">
+        <v>46207</v>
+      </c>
+      <c r="B1369" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1369" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1369">
+        <v>29</v>
+      </c>
+      <c r="E1369">
+        <v>27</v>
+      </c>
+      <c r="F1369" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1370" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1370" s="1">
+        <v>46207</v>
+      </c>
+      <c r="B1370" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1370" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1370">
+        <v>8</v>
+      </c>
+      <c r="E1370">
+        <v>8</v>
+      </c>
+      <c r="F1370" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1371" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1371" s="1">
+        <v>46207</v>
+      </c>
+      <c r="B1371" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1371" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1371">
+        <v>11</v>
+      </c>
+      <c r="E1371">
+        <v>10</v>
+      </c>
+      <c r="F1371" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1372" s="1">
+        <v>46207</v>
+      </c>
+      <c r="B1372" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1372" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1372">
+        <v>2</v>
+      </c>
+      <c r="E1372">
+        <v>2</v>
+      </c>
+      <c r="F1372" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1373" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1373" s="1">
+        <v>46207</v>
+      </c>
+      <c r="B1373" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1373" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1373">
+        <v>2</v>
+      </c>
+      <c r="E1373">
+        <v>2</v>
+      </c>
+      <c r="F1373" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1374" s="1">
+        <v>46207</v>
+      </c>
+      <c r="B1374" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1374" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1374">
+        <v>9</v>
+      </c>
+      <c r="E1374">
+        <v>9</v>
+      </c>
+      <c r="F1374" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1375" s="1">
+        <v>46207</v>
+      </c>
+      <c r="B1375" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1375" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1375">
+        <v>1</v>
+      </c>
+      <c r="E1375">
+        <v>1</v>
+      </c>
+      <c r="F1375" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1376" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1376" s="1">
+        <v>46207</v>
+      </c>
+      <c r="B1376" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1376" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1376">
+        <v>4</v>
+      </c>
+      <c r="E1376">
+        <v>4</v>
+      </c>
+      <c r="F1376" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1377" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1377" s="1">
+        <v>46207</v>
+      </c>
+      <c r="B1377" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1377" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1377">
+        <v>8</v>
+      </c>
+      <c r="E1377">
+        <v>8</v>
+      </c>
+      <c r="F1377" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1378" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1378" s="1">
+        <v>46207</v>
+      </c>
+      <c r="B1378" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1378" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1378">
+        <v>1</v>
+      </c>
+      <c r="E1378">
+        <v>1</v>
+      </c>
+      <c r="F1378" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1379" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1379" s="1">
+        <v>46207</v>
+      </c>
+      <c r="B1379" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1379" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1379">
+        <v>2</v>
+      </c>
+      <c r="E1379">
+        <v>2</v>
+      </c>
+      <c r="F1379" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1380" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1380" s="1">
+        <v>46207</v>
+      </c>
+      <c r="B1380" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1380" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1380">
+        <v>17</v>
+      </c>
+      <c r="E1380">
+        <v>17</v>
+      </c>
+      <c r="F1380" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1381" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1381" s="1">
+        <v>46207</v>
+      </c>
+      <c r="B1381" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1381" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1381">
+        <v>1</v>
+      </c>
+      <c r="E1381">
+        <v>1</v>
+      </c>
+      <c r="F1381" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1382" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1382" s="1">
+        <v>46207</v>
+      </c>
+      <c r="B1382" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1382" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1382">
+        <v>7</v>
+      </c>
+      <c r="E1382">
+        <v>3</v>
+      </c>
+      <c r="F1382" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1223" xr:uid="{22A7DA2E-DF85-4559-9E8B-F6EDBCD02D26}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\used_cars_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7576E54E-07EF-4776-98A0-45176192C974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{960CDB4C-3D3C-4A7C-B97E-BDD6462BBE1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D7CE9FC5-F49F-40D4-93B4-AA39BB343A99}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4149" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4200" uniqueCount="21">
   <si>
     <t>Date</t>
   </si>
@@ -477,7 +477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22A7DA2E-DF85-4559-9E8B-F6EDBCD02D26}">
-  <dimension ref="A1:F1382"/>
+  <dimension ref="A1:F1399"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -28125,6 +28125,346 @@
         <v>10</v>
       </c>
     </row>
+    <row r="1383" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1383" s="1">
+        <v>46208</v>
+      </c>
+      <c r="B1383" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1383" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1383">
+        <v>17</v>
+      </c>
+      <c r="E1383">
+        <v>15</v>
+      </c>
+      <c r="F1383" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1384" s="1">
+        <v>46208</v>
+      </c>
+      <c r="B1384" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1384" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1384">
+        <v>11</v>
+      </c>
+      <c r="E1384">
+        <v>10</v>
+      </c>
+      <c r="F1384" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1385" s="1">
+        <v>46208</v>
+      </c>
+      <c r="B1385" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1385" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1385">
+        <v>10</v>
+      </c>
+      <c r="E1385">
+        <v>9</v>
+      </c>
+      <c r="F1385" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1386" s="1">
+        <v>46208</v>
+      </c>
+      <c r="B1386" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1386" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1386">
+        <v>21</v>
+      </c>
+      <c r="E1386">
+        <v>18</v>
+      </c>
+      <c r="F1386" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1387" s="1">
+        <v>46208</v>
+      </c>
+      <c r="B1387" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1387" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1387">
+        <v>14</v>
+      </c>
+      <c r="E1387">
+        <v>10</v>
+      </c>
+      <c r="F1387" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1388" s="1">
+        <v>46208</v>
+      </c>
+      <c r="B1388" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1388" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1388">
+        <v>8</v>
+      </c>
+      <c r="E1388">
+        <v>8</v>
+      </c>
+      <c r="F1388" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1389" s="1">
+        <v>46208</v>
+      </c>
+      <c r="B1389" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1389" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1389">
+        <v>4</v>
+      </c>
+      <c r="E1389">
+        <v>4</v>
+      </c>
+      <c r="F1389" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1390" s="1">
+        <v>46208</v>
+      </c>
+      <c r="B1390" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1390" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1390">
+        <v>1</v>
+      </c>
+      <c r="E1390">
+        <v>1</v>
+      </c>
+      <c r="F1390" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1391" s="1">
+        <v>46208</v>
+      </c>
+      <c r="B1391" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1391" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1391">
+        <v>28</v>
+      </c>
+      <c r="E1391">
+        <v>23</v>
+      </c>
+      <c r="F1391" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1392" s="1">
+        <v>46208</v>
+      </c>
+      <c r="B1392" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1392" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1392">
+        <v>10</v>
+      </c>
+      <c r="E1392">
+        <v>10</v>
+      </c>
+      <c r="F1392" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1393" s="1">
+        <v>46208</v>
+      </c>
+      <c r="B1393" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1393" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1393">
+        <v>8</v>
+      </c>
+      <c r="E1393">
+        <v>4</v>
+      </c>
+      <c r="F1393" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1394" s="1">
+        <v>46208</v>
+      </c>
+      <c r="B1394" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1394" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1394">
+        <v>30</v>
+      </c>
+      <c r="E1394">
+        <v>30</v>
+      </c>
+      <c r="F1394" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1395" s="1">
+        <v>46208</v>
+      </c>
+      <c r="B1395" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1395" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1395">
+        <v>2</v>
+      </c>
+      <c r="E1395">
+        <v>2</v>
+      </c>
+      <c r="F1395" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1396" s="1">
+        <v>46208</v>
+      </c>
+      <c r="B1396" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1396" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1396">
+        <v>2</v>
+      </c>
+      <c r="E1396">
+        <v>2</v>
+      </c>
+      <c r="F1396" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1397" s="1">
+        <v>46208</v>
+      </c>
+      <c r="B1397" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1397" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1397">
+        <v>13</v>
+      </c>
+      <c r="E1397">
+        <v>13</v>
+      </c>
+      <c r="F1397" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1398" s="1">
+        <v>46208</v>
+      </c>
+      <c r="B1398" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1398" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1398">
+        <v>1</v>
+      </c>
+      <c r="E1398">
+        <v>1</v>
+      </c>
+      <c r="F1398" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1399" s="1">
+        <v>46208</v>
+      </c>
+      <c r="B1399" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1399" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1399">
+        <v>2</v>
+      </c>
+      <c r="E1399">
+        <v>2</v>
+      </c>
+      <c r="F1399" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1223" xr:uid="{22A7DA2E-DF85-4559-9E8B-F6EDBCD02D26}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\used_cars_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{960CDB4C-3D3C-4A7C-B97E-BDD6462BBE1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41D16DF7-7DF1-40A3-AE9E-98AEF61A7955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D7CE9FC5-F49F-40D4-93B4-AA39BB343A99}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4200" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4251" uniqueCount="21">
   <si>
     <t>Date</t>
   </si>
@@ -477,7 +477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22A7DA2E-DF85-4559-9E8B-F6EDBCD02D26}">
-  <dimension ref="A1:F1399"/>
+  <dimension ref="A1:F1416"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -28465,6 +28465,346 @@
         <v>10</v>
       </c>
     </row>
+    <row r="1400" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1400" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B1400" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1400" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1400">
+        <v>28</v>
+      </c>
+      <c r="E1400">
+        <v>24</v>
+      </c>
+      <c r="F1400" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1401" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B1401" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1401" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1401">
+        <v>6</v>
+      </c>
+      <c r="E1401">
+        <v>6</v>
+      </c>
+      <c r="F1401" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1402" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B1402" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1402" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1402">
+        <v>17</v>
+      </c>
+      <c r="E1402">
+        <v>9</v>
+      </c>
+      <c r="F1402" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1403" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B1403" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1403" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1403">
+        <v>28</v>
+      </c>
+      <c r="E1403">
+        <v>26</v>
+      </c>
+      <c r="F1403" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1404" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B1404" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1404" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1404">
+        <v>7</v>
+      </c>
+      <c r="E1404">
+        <v>7</v>
+      </c>
+      <c r="F1404" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1405" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B1405" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1405" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1405">
+        <v>14</v>
+      </c>
+      <c r="E1405">
+        <v>11</v>
+      </c>
+      <c r="F1405" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1406" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B1406" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1406" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1406">
+        <v>3</v>
+      </c>
+      <c r="E1406">
+        <v>3</v>
+      </c>
+      <c r="F1406" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1407" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B1407" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1407" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1407">
+        <v>1</v>
+      </c>
+      <c r="E1407">
+        <v>1</v>
+      </c>
+      <c r="F1407" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1408" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B1408" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1408" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1408">
+        <v>7</v>
+      </c>
+      <c r="E1408">
+        <v>5</v>
+      </c>
+      <c r="F1408" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1409" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B1409" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1409" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1409">
+        <v>10</v>
+      </c>
+      <c r="E1409">
+        <v>9</v>
+      </c>
+      <c r="F1409" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1410" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B1410" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1410" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1410">
+        <v>2</v>
+      </c>
+      <c r="E1410">
+        <v>2</v>
+      </c>
+      <c r="F1410" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1411" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B1411" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1411" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1411">
+        <v>6</v>
+      </c>
+      <c r="E1411">
+        <v>2</v>
+      </c>
+      <c r="F1411" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1412" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B1412" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1412" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1412">
+        <v>14</v>
+      </c>
+      <c r="E1412">
+        <v>14</v>
+      </c>
+      <c r="F1412" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1413" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B1413" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1413" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1413">
+        <v>1</v>
+      </c>
+      <c r="E1413">
+        <v>1</v>
+      </c>
+      <c r="F1413" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1414" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B1414" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1414" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1414">
+        <v>2</v>
+      </c>
+      <c r="E1414">
+        <v>2</v>
+      </c>
+      <c r="F1414" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1415" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B1415" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1415" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1415">
+        <v>16</v>
+      </c>
+      <c r="E1415">
+        <v>15</v>
+      </c>
+      <c r="F1415" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1416" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B1416" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1416" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1416">
+        <v>5</v>
+      </c>
+      <c r="E1416">
+        <v>5</v>
+      </c>
+      <c r="F1416" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1223" xr:uid="{22A7DA2E-DF85-4559-9E8B-F6EDBCD02D26}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
